--- a/research/traditional_assets/database/data/philippines/philippines_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_retail_distributors.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08556362689569728</v>
+        <v>0.08538346782845804</v>
       </c>
       <c r="C2">
-        <v>175.2825264951105</v>
+        <v>174.2293581772846</v>
       </c>
       <c r="D2">
-        <v>153.9825264951105</v>
+        <v>154.6833581772846</v>
       </c>
       <c r="E2">
-        <v>-43.3</v>
+        <v>-41.546</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.754</v>
       </c>
       <c r="G2">
         <v>21.3</v>
@@ -1451,28 +1451,28 @@
         <v>4.927</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08822619999999999</v>
       </c>
       <c r="N2">
-        <v>4.927</v>
+        <v>4.838773799999999</v>
       </c>
       <c r="O2">
-        <v>1.23175</v>
+        <v>1.20969345</v>
       </c>
       <c r="P2">
-        <v>3.69525</v>
+        <v>3.62908035</v>
       </c>
       <c r="Q2">
-        <v>4.56825</v>
+        <v>4.50208035</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08556362689569728</v>
+        <v>0.08586486649339196</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381922</v>
+        <v>0.5829926250339361</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>55.84508910051662</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08538346782845804</v>
+        <v>0.0852033087612188</v>
       </c>
       <c r="C3">
-        <v>174.2293581772846</v>
+        <v>173.1825985183313</v>
       </c>
       <c r="D3">
-        <v>154.6833581772846</v>
+        <v>155.3905985183313</v>
       </c>
       <c r="E3">
-        <v>-41.546</v>
+        <v>-39.79199999999999</v>
       </c>
       <c r="F3">
-        <v>1.754</v>
+        <v>3.508</v>
       </c>
       <c r="G3">
         <v>21.3</v>
@@ -1533,28 +1533,28 @@
         <v>4.927</v>
       </c>
       <c r="M3">
-        <v>0.08822619999999999</v>
+        <v>0.1764524</v>
       </c>
       <c r="N3">
-        <v>4.838773799999999</v>
+        <v>4.7505476</v>
       </c>
       <c r="O3">
-        <v>1.20969345</v>
+        <v>1.1876369</v>
       </c>
       <c r="P3">
-        <v>3.62908035</v>
+        <v>3.5629107</v>
       </c>
       <c r="Q3">
-        <v>4.50208035</v>
+        <v>4.4359107</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08586486649339196</v>
+        <v>0.08617225383797837</v>
       </c>
       <c r="T3">
-        <v>0.5829926250339361</v>
+        <v>0.5874654854377565</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>55.84508910051662</v>
+        <v>27.92254455025832</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0852033087612188</v>
+        <v>0.08502314969397953</v>
       </c>
       <c r="C4">
-        <v>173.1825985183313</v>
+        <v>172.1423358266615</v>
       </c>
       <c r="D4">
-        <v>155.3905985183313</v>
+        <v>156.1043358266615</v>
       </c>
       <c r="E4">
-        <v>-39.79199999999999</v>
+        <v>-38.038</v>
       </c>
       <c r="F4">
-        <v>3.508</v>
+        <v>5.262</v>
       </c>
       <c r="G4">
         <v>21.3</v>
@@ -1615,28 +1615,28 @@
         <v>4.927</v>
       </c>
       <c r="M4">
-        <v>0.1764524</v>
+        <v>0.2646786</v>
       </c>
       <c r="N4">
-        <v>4.7505476</v>
+        <v>4.6623214</v>
       </c>
       <c r="O4">
-        <v>1.1876369</v>
+        <v>1.16558035</v>
       </c>
       <c r="P4">
-        <v>3.5629107</v>
+        <v>3.49674105</v>
       </c>
       <c r="Q4">
-        <v>4.4359107</v>
+        <v>4.36974105</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08617225383797837</v>
+        <v>0.08648597906595828</v>
       </c>
       <c r="T4">
-        <v>0.5874654854377565</v>
+        <v>0.5920305697674285</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>27.92254455025832</v>
+        <v>18.61502970017221</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08502314969397953</v>
+        <v>0.08484299062674031</v>
       </c>
       <c r="C5">
-        <v>172.1423358266615</v>
+        <v>171.1086600406388</v>
       </c>
       <c r="D5">
-        <v>156.1043358266615</v>
+        <v>156.8246600406388</v>
       </c>
       <c r="E5">
-        <v>-38.038</v>
+        <v>-36.284</v>
       </c>
       <c r="F5">
-        <v>5.262</v>
+        <v>7.015999999999999</v>
       </c>
       <c r="G5">
         <v>21.3</v>
@@ -1697,28 +1697,28 @@
         <v>4.927</v>
       </c>
       <c r="M5">
-        <v>0.2646786</v>
+        <v>0.3529048</v>
       </c>
       <c r="N5">
-        <v>4.6623214</v>
+        <v>4.574095199999999</v>
       </c>
       <c r="O5">
-        <v>1.16558035</v>
+        <v>1.1435238</v>
       </c>
       <c r="P5">
-        <v>3.49674105</v>
+        <v>3.4305714</v>
       </c>
       <c r="Q5">
-        <v>4.36974105</v>
+        <v>4.3035714</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08648597906595828</v>
+        <v>0.08680624023618783</v>
       </c>
       <c r="T5">
-        <v>0.5920305697674285</v>
+        <v>0.5966907600206357</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>18.61502970017221</v>
+        <v>13.96127227512916</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08484299062674031</v>
+        <v>0.08471908155950106</v>
       </c>
       <c r="C6">
-        <v>171.1086600406388</v>
+        <v>169.8539523303615</v>
       </c>
       <c r="D6">
-        <v>156.8246600406388</v>
+        <v>157.3239523303615</v>
       </c>
       <c r="E6">
-        <v>-36.284</v>
+        <v>-34.53</v>
       </c>
       <c r="F6">
-        <v>7.015999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="G6">
         <v>21.3</v>
@@ -1779,45 +1779,45 @@
         <v>4.927</v>
       </c>
       <c r="M6">
-        <v>0.3529048</v>
+        <v>0.454286</v>
       </c>
       <c r="N6">
-        <v>4.574095199999999</v>
+        <v>4.472714</v>
       </c>
       <c r="O6">
-        <v>1.1435238</v>
+        <v>1.1181785</v>
       </c>
       <c r="P6">
-        <v>3.4305714</v>
+        <v>3.3545355</v>
       </c>
       <c r="Q6">
-        <v>4.3035714</v>
+        <v>4.2275355</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08680624023618783</v>
+        <v>0.08713324374684323</v>
       </c>
       <c r="T6">
-        <v>0.5966907600206357</v>
+        <v>0.6014490595423314</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>13.96127227512916</v>
+        <v>10.84559066315053</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08471908155950106</v>
+        <v>0.08462667249226183</v>
       </c>
       <c r="C7">
-        <v>169.8539523303615</v>
+        <v>168.4743897661766</v>
       </c>
       <c r="D7">
-        <v>157.3239523303615</v>
+        <v>157.6983897661766</v>
       </c>
       <c r="E7">
-        <v>-34.53</v>
+        <v>-32.776</v>
       </c>
       <c r="F7">
-        <v>8.77</v>
+        <v>10.524</v>
       </c>
       <c r="G7">
         <v>21.3</v>
@@ -1861,45 +1861,45 @@
         <v>4.927</v>
       </c>
       <c r="M7">
-        <v>0.454286</v>
+        <v>0.5630339999999999</v>
       </c>
       <c r="N7">
-        <v>4.472714</v>
+        <v>4.363966</v>
       </c>
       <c r="O7">
-        <v>1.1181785</v>
+        <v>1.0909915</v>
       </c>
       <c r="P7">
-        <v>3.3545355</v>
+        <v>3.2729745</v>
       </c>
       <c r="Q7">
-        <v>4.2275355</v>
+        <v>4.145974499999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08713324374684323</v>
+        <v>0.08746720477900194</v>
       </c>
       <c r="T7">
-        <v>0.6014490595423314</v>
+        <v>0.6063085994793822</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.84559066315053</v>
+        <v>8.750803681482823</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08462667249226183</v>
+        <v>0.08451251342502258</v>
       </c>
       <c r="C8">
-        <v>168.4743897661766</v>
+        <v>167.1854254739642</v>
       </c>
       <c r="D8">
-        <v>157.6983897661766</v>
+        <v>158.1634254739641</v>
       </c>
       <c r="E8">
-        <v>-32.776</v>
+        <v>-31.022</v>
       </c>
       <c r="F8">
-        <v>10.524</v>
+        <v>12.278</v>
       </c>
       <c r="G8">
         <v>21.3</v>
@@ -1943,45 +1943,45 @@
         <v>4.927</v>
       </c>
       <c r="M8">
-        <v>0.5630339999999999</v>
+        <v>0.6666953999999998</v>
       </c>
       <c r="N8">
-        <v>4.363966</v>
+        <v>4.2603046</v>
       </c>
       <c r="O8">
-        <v>1.0909915</v>
+        <v>1.06507615</v>
       </c>
       <c r="P8">
-        <v>3.2729745</v>
+        <v>3.19522845</v>
       </c>
       <c r="Q8">
-        <v>4.145974499999999</v>
+        <v>4.068228449999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08746720477900194</v>
+        <v>0.08780834776884149</v>
       </c>
       <c r="T8">
-        <v>0.6063085994793822</v>
+        <v>0.6112726456516385</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>8.750803681482823</v>
+        <v>7.390181483178076</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08451251342502257</v>
+        <v>0.08436235435778335</v>
       </c>
       <c r="C9">
-        <v>167.1854254739642</v>
+        <v>166.047302612071</v>
       </c>
       <c r="D9">
-        <v>158.1634254739642</v>
+        <v>158.779302612071</v>
       </c>
       <c r="E9">
-        <v>-31.022</v>
+        <v>-29.268</v>
       </c>
       <c r="F9">
-        <v>12.278</v>
+        <v>14.032</v>
       </c>
       <c r="G9">
         <v>21.3</v>
@@ -2025,28 +2025,28 @@
         <v>4.927</v>
       </c>
       <c r="M9">
-        <v>0.6666953999999999</v>
+        <v>0.7619375999999999</v>
       </c>
       <c r="N9">
-        <v>4.2603046</v>
+        <v>4.1650624</v>
       </c>
       <c r="O9">
-        <v>1.06507615</v>
+        <v>1.0412656</v>
       </c>
       <c r="P9">
-        <v>3.19522845</v>
+        <v>3.1237968</v>
       </c>
       <c r="Q9">
-        <v>4.068228449999999</v>
+        <v>3.9967968</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08780834776884149</v>
+        <v>0.08815690691063408</v>
       </c>
       <c r="T9">
-        <v>0.6112726456516385</v>
+        <v>0.6163446058711178</v>
       </c>
       <c r="U9">
         <v>0.0543</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>7.390181483178075</v>
+        <v>6.466408797780817</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08436235435778335</v>
+        <v>0.08427969529054409</v>
       </c>
       <c r="C10">
-        <v>166.047302612071</v>
+        <v>164.6343798724732</v>
       </c>
       <c r="D10">
-        <v>158.779302612071</v>
+        <v>159.1203798724732</v>
       </c>
       <c r="E10">
-        <v>-29.268</v>
+        <v>-27.514</v>
       </c>
       <c r="F10">
-        <v>14.032</v>
+        <v>15.786</v>
       </c>
       <c r="G10">
         <v>21.3</v>
@@ -2107,45 +2107,45 @@
         <v>4.927</v>
       </c>
       <c r="M10">
-        <v>0.7619375999999999</v>
+        <v>0.8729657999999999</v>
       </c>
       <c r="N10">
-        <v>4.1650624</v>
+        <v>4.054034199999999</v>
       </c>
       <c r="O10">
-        <v>1.0412656</v>
+        <v>1.01350855</v>
       </c>
       <c r="P10">
-        <v>3.1237968</v>
+        <v>3.040525649999999</v>
       </c>
       <c r="Q10">
-        <v>3.9967968</v>
+        <v>3.91352565</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08815690691063408</v>
+        <v>0.08851312669290559</v>
       </c>
       <c r="T10">
-        <v>0.6163446058711178</v>
+        <v>0.6215280377437724</v>
       </c>
       <c r="U10">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>6.466408797780817</v>
+        <v>5.643978263524184</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08427969529054409</v>
+        <v>0.08413703622330486</v>
       </c>
       <c r="C11">
-        <v>164.6343798724732</v>
+        <v>163.4724956750391</v>
       </c>
       <c r="D11">
-        <v>159.1203798724732</v>
+        <v>159.7124956750391</v>
       </c>
       <c r="E11">
-        <v>-27.514</v>
+        <v>-25.76</v>
       </c>
       <c r="F11">
-        <v>15.786</v>
+        <v>17.54</v>
       </c>
       <c r="G11">
         <v>21.3</v>
@@ -2189,28 +2189,28 @@
         <v>4.927</v>
       </c>
       <c r="M11">
-        <v>0.8729657999999999</v>
+        <v>0.9699619999999998</v>
       </c>
       <c r="N11">
-        <v>4.054034199999999</v>
+        <v>3.957038</v>
       </c>
       <c r="O11">
-        <v>1.01350855</v>
+        <v>0.9892595</v>
       </c>
       <c r="P11">
-        <v>3.040525649999999</v>
+        <v>2.9677785</v>
       </c>
       <c r="Q11">
-        <v>3.91352565</v>
+        <v>3.8407785</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08851312669290559</v>
+        <v>0.08887726247033872</v>
       </c>
       <c r="T11">
-        <v>0.6215280377437724</v>
+        <v>0.6268266569913749</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.643978263524184</v>
+        <v>5.079580437171766</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08413703622330486</v>
+        <v>0.08399437715606563</v>
       </c>
       <c r="C12">
-        <v>163.4724956750391</v>
+        <v>162.3150346777921</v>
       </c>
       <c r="D12">
-        <v>159.7124956750391</v>
+        <v>160.3090346777921</v>
       </c>
       <c r="E12">
-        <v>-25.76</v>
+        <v>-24.006</v>
       </c>
       <c r="F12">
-        <v>17.54</v>
+        <v>19.294</v>
       </c>
       <c r="G12">
         <v>21.3</v>
@@ -2271,28 +2271,28 @@
         <v>4.927</v>
       </c>
       <c r="M12">
-        <v>0.969962</v>
+        <v>1.0669582</v>
       </c>
       <c r="N12">
-        <v>3.957038</v>
+        <v>3.860041799999999</v>
       </c>
       <c r="O12">
-        <v>0.9892595</v>
+        <v>0.9650104499999999</v>
       </c>
       <c r="P12">
-        <v>2.9677785</v>
+        <v>2.89503135</v>
       </c>
       <c r="Q12">
-        <v>3.8407785</v>
+        <v>3.768031349999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08887726247033872</v>
+        <v>0.08924958107423103</v>
       </c>
       <c r="T12">
-        <v>0.6268266569913749</v>
+        <v>0.6322443463344292</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.079580437171765</v>
+        <v>4.617800397428877</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08399437715606563</v>
+        <v>0.08407671808882636</v>
       </c>
       <c r="C13">
-        <v>162.3150346777921</v>
+        <v>160.216177644472</v>
       </c>
       <c r="D13">
-        <v>160.3090346777921</v>
+        <v>159.964177644472</v>
       </c>
       <c r="E13">
-        <v>-24.006</v>
+        <v>-22.252</v>
       </c>
       <c r="F13">
-        <v>19.294</v>
+        <v>21.048</v>
       </c>
       <c r="G13">
         <v>21.3</v>
@@ -2353,45 +2353,45 @@
         <v>4.927</v>
       </c>
       <c r="M13">
-        <v>1.0669582</v>
+        <v>1.2165744</v>
       </c>
       <c r="N13">
-        <v>3.860041799999999</v>
+        <v>3.7104256</v>
       </c>
       <c r="O13">
-        <v>0.9650104499999999</v>
+        <v>0.9276063999999999</v>
       </c>
       <c r="P13">
-        <v>2.89503135</v>
+        <v>2.7828192</v>
       </c>
       <c r="Q13">
-        <v>3.768031349999999</v>
+        <v>3.6558192</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08924958107423103</v>
+        <v>0.08963036146457541</v>
       </c>
       <c r="T13">
-        <v>0.6322443463344292</v>
+        <v>0.6377851649807346</v>
       </c>
       <c r="U13">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.617800397428877</v>
+        <v>4.049896167468262</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08407671808882636</v>
+        <v>0.08429405902158713</v>
       </c>
       <c r="C14">
-        <v>160.216177644472</v>
+        <v>157.5590054547567</v>
       </c>
       <c r="D14">
-        <v>159.964177644472</v>
+        <v>159.0610054547567</v>
       </c>
       <c r="E14">
-        <v>-22.252</v>
+        <v>-20.498</v>
       </c>
       <c r="F14">
-        <v>21.048</v>
+        <v>22.802</v>
       </c>
       <c r="G14">
         <v>21.3</v>
@@ -2435,45 +2435,45 @@
         <v>4.927</v>
       </c>
       <c r="M14">
-        <v>1.2165744</v>
+        <v>1.3977626</v>
       </c>
       <c r="N14">
-        <v>3.7104256</v>
+        <v>3.5292374</v>
       </c>
       <c r="O14">
-        <v>0.9276063999999999</v>
+        <v>0.8823093499999999</v>
       </c>
       <c r="P14">
-        <v>2.7828192</v>
+        <v>2.64692805</v>
       </c>
       <c r="Q14">
-        <v>3.6558192</v>
+        <v>3.51992805</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08963036146457541</v>
+        <v>0.09001989542711164</v>
       </c>
       <c r="T14">
-        <v>0.6377851649807346</v>
+        <v>0.6434533587683344</v>
       </c>
       <c r="U14">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.049896167468262</v>
+        <v>3.52491903846905</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08429405902158713</v>
+        <v>0.08449039995434787</v>
       </c>
       <c r="C15">
-        <v>157.5590054547567</v>
+        <v>154.9978236677062</v>
       </c>
       <c r="D15">
-        <v>159.0610054547567</v>
+        <v>158.2538236677062</v>
       </c>
       <c r="E15">
-        <v>-20.498</v>
+        <v>-18.744</v>
       </c>
       <c r="F15">
-        <v>22.802</v>
+        <v>24.556</v>
       </c>
       <c r="G15">
         <v>21.3</v>
@@ -2517,45 +2517,45 @@
         <v>4.927</v>
       </c>
       <c r="M15">
-        <v>1.3977626</v>
+        <v>1.5740396</v>
       </c>
       <c r="N15">
-        <v>3.5292374</v>
+        <v>3.3529604</v>
       </c>
       <c r="O15">
-        <v>0.8823093499999999</v>
+        <v>0.8382400999999999</v>
       </c>
       <c r="P15">
-        <v>2.64692805</v>
+        <v>2.5147203</v>
       </c>
       <c r="Q15">
-        <v>3.51992805</v>
+        <v>3.3877203</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09001989542711164</v>
+        <v>0.09041848831900916</v>
       </c>
       <c r="T15">
-        <v>0.6434533587683344</v>
+        <v>0.649253371016111</v>
       </c>
       <c r="U15">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.52491903846905</v>
+        <v>3.130162671892117</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08449039995434787</v>
+        <v>0.08529124088710864</v>
       </c>
       <c r="C16">
-        <v>154.9978236677062</v>
+        <v>150.0346021565033</v>
       </c>
       <c r="D16">
-        <v>158.2538236677062</v>
+        <v>155.0446021565033</v>
       </c>
       <c r="E16">
-        <v>-18.744</v>
+        <v>-16.99</v>
       </c>
       <c r="F16">
-        <v>24.556</v>
+        <v>26.31</v>
       </c>
       <c r="G16">
         <v>21.3</v>
@@ -2599,45 +2599,45 @@
         <v>4.927</v>
       </c>
       <c r="M16">
-        <v>1.5740396</v>
+        <v>1.891689</v>
       </c>
       <c r="N16">
-        <v>3.3529604</v>
+        <v>3.035311</v>
       </c>
       <c r="O16">
-        <v>0.8382400999999999</v>
+        <v>0.7588277499999999</v>
       </c>
       <c r="P16">
-        <v>2.5147203</v>
+        <v>2.27648325</v>
       </c>
       <c r="Q16">
-        <v>3.3877203</v>
+        <v>3.149483249999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09041848831900916</v>
+        <v>0.09082645986718663</v>
       </c>
       <c r="T16">
-        <v>0.649253371016111</v>
+        <v>0.6551898541403058</v>
       </c>
       <c r="U16">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.130162671892117</v>
+        <v>2.604550748035221</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08529124088710864</v>
+        <v>0.08574108181986938</v>
       </c>
       <c r="C17">
-        <v>150.0346021565033</v>
+        <v>146.5343948612642</v>
       </c>
       <c r="D17">
-        <v>155.0446021565033</v>
+        <v>153.2983948612642</v>
       </c>
       <c r="E17">
-        <v>-16.99</v>
+        <v>-15.236</v>
       </c>
       <c r="F17">
-        <v>26.31</v>
+        <v>28.064</v>
       </c>
       <c r="G17">
         <v>21.3</v>
@@ -2681,45 +2681,45 @@
         <v>4.927</v>
       </c>
       <c r="M17">
-        <v>1.891689</v>
+        <v>2.1272512</v>
       </c>
       <c r="N17">
-        <v>3.035311</v>
+        <v>2.7997488</v>
       </c>
       <c r="O17">
-        <v>0.75882775</v>
+        <v>0.6999371999999999</v>
       </c>
       <c r="P17">
-        <v>2.27648325</v>
+        <v>2.0998116</v>
       </c>
       <c r="Q17">
-        <v>3.14948325</v>
+        <v>2.9728116</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09082645986718663</v>
+        <v>0.09124414502365402</v>
       </c>
       <c r="T17">
-        <v>0.6551898541403058</v>
+        <v>0.661267682100791</v>
       </c>
       <c r="U17">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.604550748035222</v>
+        <v>2.316134549600912</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08574108181986938</v>
+        <v>0.08575217275263015</v>
       </c>
       <c r="C18">
-        <v>146.5343948612642</v>
+        <v>144.7378384225877</v>
       </c>
       <c r="D18">
-        <v>153.2983948612642</v>
+        <v>153.2558384225877</v>
       </c>
       <c r="E18">
-        <v>-15.236</v>
+        <v>-13.482</v>
       </c>
       <c r="F18">
-        <v>28.064</v>
+        <v>29.818</v>
       </c>
       <c r="G18">
         <v>21.3</v>
@@ -2763,28 +2763,28 @@
         <v>4.927</v>
       </c>
       <c r="M18">
-        <v>2.1272512</v>
+        <v>2.2602044</v>
       </c>
       <c r="N18">
-        <v>2.7997488</v>
+        <v>2.666795599999999</v>
       </c>
       <c r="O18">
-        <v>0.6999371999999999</v>
+        <v>0.6666988999999999</v>
       </c>
       <c r="P18">
-        <v>2.0998116</v>
+        <v>2.000096699999999</v>
       </c>
       <c r="Q18">
-        <v>2.9728116</v>
+        <v>2.8730967</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09124414502365402</v>
+        <v>0.09167189488268693</v>
       </c>
       <c r="T18">
-        <v>0.661267682100791</v>
+        <v>0.6674919637470712</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.316134549600912</v>
+        <v>2.179891340800858</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08575217275263015</v>
+        <v>0.0857632636853909</v>
       </c>
       <c r="C19">
-        <v>144.7378384225877</v>
+        <v>142.9413056051351</v>
       </c>
       <c r="D19">
-        <v>153.2558384225877</v>
+        <v>153.2133056051351</v>
       </c>
       <c r="E19">
-        <v>-13.482</v>
+        <v>-11.728</v>
       </c>
       <c r="F19">
-        <v>29.818</v>
+        <v>31.572</v>
       </c>
       <c r="G19">
         <v>21.3</v>
@@ -2845,28 +2845,28 @@
         <v>4.927</v>
       </c>
       <c r="M19">
-        <v>2.2602044</v>
+        <v>2.3931576</v>
       </c>
       <c r="N19">
-        <v>2.666795599999999</v>
+        <v>2.533842399999999</v>
       </c>
       <c r="O19">
-        <v>0.6666988999999999</v>
+        <v>0.6334605999999998</v>
       </c>
       <c r="P19">
-        <v>2.000096699999999</v>
+        <v>1.900381799999999</v>
       </c>
       <c r="Q19">
-        <v>2.8730967</v>
+        <v>2.773381799999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09167189488268693</v>
+        <v>0.09211007766511085</v>
       </c>
       <c r="T19">
-        <v>0.6674919637470712</v>
+        <v>0.6738680571408213</v>
       </c>
       <c r="U19">
         <v>0.07580000000000001</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>2.179891340800858</v>
+        <v>2.058786266311921</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08576326368539092</v>
+        <v>0.08779785461815166</v>
       </c>
       <c r="C20">
-        <v>142.9413056051351</v>
+        <v>133.7648692641183</v>
       </c>
       <c r="D20">
-        <v>153.2133056051351</v>
+        <v>145.7908692641183</v>
       </c>
       <c r="E20">
-        <v>-11.728</v>
+        <v>-9.974000000000004</v>
       </c>
       <c r="F20">
-        <v>31.572</v>
+        <v>33.32599999999999</v>
       </c>
       <c r="G20">
         <v>21.3</v>
@@ -2927,45 +2927,45 @@
         <v>4.927</v>
       </c>
       <c r="M20">
-        <v>2.3931576</v>
+        <v>2.999339999999999</v>
       </c>
       <c r="N20">
-        <v>2.5338424</v>
+        <v>1.92766</v>
       </c>
       <c r="O20">
-        <v>0.6334605999999999</v>
+        <v>0.4819150000000001</v>
       </c>
       <c r="P20">
-        <v>1.9003818</v>
+        <v>1.445745</v>
       </c>
       <c r="Q20">
-        <v>2.7733818</v>
+        <v>2.318745</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09211007766511085</v>
+        <v>0.09255907977549588</v>
       </c>
       <c r="T20">
-        <v>0.6738680571408213</v>
+        <v>0.6804015849393557</v>
       </c>
       <c r="U20">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.058786266311922</v>
+        <v>1.642694726173092</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08779785461815166</v>
+        <v>0.08791544555091242</v>
       </c>
       <c r="C21">
-        <v>133.7648692641183</v>
+        <v>131.6038052029286</v>
       </c>
       <c r="D21">
-        <v>145.7908692641183</v>
+        <v>145.3838052029286</v>
       </c>
       <c r="E21">
-        <v>-9.974000000000004</v>
+        <v>-8.219999999999999</v>
       </c>
       <c r="F21">
-        <v>33.32599999999999</v>
+        <v>35.08</v>
       </c>
       <c r="G21">
         <v>21.3</v>
@@ -3009,28 +3009,28 @@
         <v>4.927</v>
       </c>
       <c r="M21">
-        <v>2.999339999999999</v>
+        <v>3.1572</v>
       </c>
       <c r="N21">
-        <v>1.92766</v>
+        <v>1.7698</v>
       </c>
       <c r="O21">
-        <v>0.4819150000000001</v>
+        <v>0.44245</v>
       </c>
       <c r="P21">
-        <v>1.445745</v>
+        <v>1.32735</v>
       </c>
       <c r="Q21">
-        <v>2.318745</v>
+        <v>2.20035</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09255907977549588</v>
+        <v>0.09301930693864052</v>
       </c>
       <c r="T21">
-        <v>0.6804015849393557</v>
+        <v>0.6870984509328533</v>
       </c>
       <c r="U21">
         <v>0.09</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>1.642694726173092</v>
+        <v>1.560559989864437</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08791544555091242</v>
+        <v>0.09784892122377359</v>
       </c>
       <c r="C22">
-        <v>131.6038052029286</v>
+        <v>102.1034762059762</v>
       </c>
       <c r="D22">
-        <v>145.3838052029286</v>
+        <v>117.6374762059762</v>
       </c>
       <c r="E22">
-        <v>-8.219999999999999</v>
+        <v>-6.466000000000001</v>
       </c>
       <c r="F22">
-        <v>35.08</v>
+        <v>36.834</v>
       </c>
       <c r="G22">
         <v>21.3</v>
@@ -3091,45 +3091,45 @@
         <v>4.927</v>
       </c>
       <c r="M22">
-        <v>3.1572</v>
+        <v>5.4072312</v>
       </c>
       <c r="N22">
-        <v>1.7698</v>
+        <v>-0.4802312000000004</v>
       </c>
       <c r="O22">
-        <v>0.44245</v>
+        <v>-0.1200578000000001</v>
       </c>
       <c r="P22">
-        <v>1.32735</v>
+        <v>-0.3601734000000003</v>
       </c>
       <c r="Q22">
-        <v>2.20035</v>
+        <v>0.5128265999999997</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09301930693864052</v>
+        <v>0.09372587490906778</v>
       </c>
       <c r="T22">
-        <v>0.6870984509328533</v>
+        <v>0.6973798758294576</v>
       </c>
       <c r="U22">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.25</v>
+        <v>0.2277968066170353</v>
       </c>
       <c r="W22">
-        <v>0.0675</v>
+        <v>0.1133594287886192</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y22">
-        <v>1.560559989864437</v>
+        <v>0.9111872264681413</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09784892122377359</v>
+        <v>0.0988589212237736</v>
       </c>
       <c r="C23">
-        <v>102.1034762059762</v>
+        <v>98.11019488951399</v>
       </c>
       <c r="D23">
-        <v>117.6374762059762</v>
+        <v>115.398194889514</v>
       </c>
       <c r="E23">
-        <v>-6.466000000000001</v>
+        <v>-4.712000000000003</v>
       </c>
       <c r="F23">
-        <v>36.834</v>
+        <v>38.58799999999999</v>
       </c>
       <c r="G23">
         <v>21.3</v>
@@ -3173,37 +3173,37 @@
         <v>4.927</v>
       </c>
       <c r="M23">
-        <v>5.4072312</v>
+        <v>5.6647184</v>
       </c>
       <c r="N23">
-        <v>-0.4802312000000004</v>
+        <v>-0.7377184000000003</v>
       </c>
       <c r="O23">
-        <v>-0.1200578000000001</v>
+        <v>-0.1844296000000001</v>
       </c>
       <c r="P23">
-        <v>-0.3601734000000003</v>
+        <v>-0.5532888000000002</v>
       </c>
       <c r="Q23">
-        <v>0.5128265999999997</v>
+        <v>0.3197111999999998</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09372587490906778</v>
+        <v>0.09434030920277378</v>
       </c>
       <c r="T23">
-        <v>0.6973798758294576</v>
+        <v>0.7063206434682968</v>
       </c>
       <c r="U23">
         <v>0.1468</v>
       </c>
       <c r="V23">
-        <v>0.2277968066170353</v>
+        <v>0.217442406316261</v>
       </c>
       <c r="W23">
-        <v>0.1133594287886192</v>
+        <v>0.1148794547527729</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.9111872264681413</v>
+        <v>0.869769625265044</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0988589212237736</v>
+        <v>0.09986892122377358</v>
       </c>
       <c r="C24">
-        <v>98.11019488951399</v>
+        <v>94.20057250607424</v>
       </c>
       <c r="D24">
-        <v>115.398194889514</v>
+        <v>113.2425725060742</v>
       </c>
       <c r="E24">
-        <v>-4.712000000000003</v>
+        <v>-2.957999999999998</v>
       </c>
       <c r="F24">
-        <v>38.58799999999999</v>
+        <v>40.342</v>
       </c>
       <c r="G24">
         <v>21.3</v>
@@ -3255,37 +3255,37 @@
         <v>4.927</v>
       </c>
       <c r="M24">
-        <v>5.6647184</v>
+        <v>5.922205600000001</v>
       </c>
       <c r="N24">
-        <v>-0.7377184000000003</v>
+        <v>-0.9952056000000011</v>
       </c>
       <c r="O24">
-        <v>-0.1844296000000001</v>
+        <v>-0.2488014000000003</v>
       </c>
       <c r="P24">
-        <v>-0.5532888000000002</v>
+        <v>-0.7464042000000009</v>
       </c>
       <c r="Q24">
-        <v>0.3197111999999998</v>
+        <v>0.1265957999999991</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09434030920277378</v>
+        <v>0.09497070282878382</v>
       </c>
       <c r="T24">
-        <v>0.7063206434682968</v>
+        <v>0.7154936388380149</v>
       </c>
       <c r="U24">
         <v>0.1468</v>
       </c>
       <c r="V24">
-        <v>0.217442406316261</v>
+        <v>0.2079883886503366</v>
       </c>
       <c r="W24">
-        <v>0.1148794547527729</v>
+        <v>0.1162673045461306</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.869769625265044</v>
+        <v>0.8319535546013463</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09986892122377358</v>
+        <v>0.1143504651916363</v>
       </c>
       <c r="C25">
-        <v>94.20057250607424</v>
+        <v>68.52365253469117</v>
       </c>
       <c r="D25">
-        <v>113.2425725060742</v>
+        <v>89.31965253469117</v>
       </c>
       <c r="E25">
-        <v>-2.957999999999998</v>
+        <v>-1.204000000000001</v>
       </c>
       <c r="F25">
-        <v>40.342</v>
+        <v>42.096</v>
       </c>
       <c r="G25">
         <v>21.3</v>
@@ -3337,45 +3337,45 @@
         <v>4.927</v>
       </c>
       <c r="M25">
-        <v>5.922205600000001</v>
+        <v>8.4528768</v>
       </c>
       <c r="N25">
-        <v>-0.9952056000000011</v>
+        <v>-3.525876800000001</v>
       </c>
       <c r="O25">
-        <v>-0.2488014000000003</v>
+        <v>-0.8814692000000002</v>
       </c>
       <c r="P25">
-        <v>-0.7464042000000009</v>
+        <v>-2.644407600000001</v>
       </c>
       <c r="Q25">
-        <v>0.1265957999999991</v>
+        <v>-1.771407600000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09497070282878382</v>
+        <v>0.09629076992898186</v>
       </c>
       <c r="T25">
-        <v>0.7154936388380149</v>
+        <v>0.7347022235987383</v>
       </c>
       <c r="U25">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.2079883886503366</v>
+        <v>0.1457196205675209</v>
       </c>
       <c r="W25">
-        <v>0.1162673045461306</v>
+        <v>0.1715395001900418</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y25">
-        <v>0.8319535546013463</v>
+        <v>0.5828784822700834</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1143504651916362</v>
+        <v>0.1159004651916362</v>
       </c>
       <c r="C26">
-        <v>68.52365253469122</v>
+        <v>64.79469472163966</v>
       </c>
       <c r="D26">
-        <v>89.31965253469123</v>
+        <v>87.34469472163966</v>
       </c>
       <c r="E26">
-        <v>-1.204000000000001</v>
+        <v>0.5499999999999972</v>
       </c>
       <c r="F26">
-        <v>42.096</v>
+        <v>43.84999999999999</v>
       </c>
       <c r="G26">
         <v>21.3</v>
@@ -3419,37 +3419,37 @@
         <v>4.927</v>
       </c>
       <c r="M26">
-        <v>8.4528768</v>
+        <v>8.805079999999998</v>
       </c>
       <c r="N26">
-        <v>-3.525876800000001</v>
+        <v>-3.878079999999999</v>
       </c>
       <c r="O26">
-        <v>-0.8814692000000002</v>
+        <v>-0.9695199999999997</v>
       </c>
       <c r="P26">
-        <v>-2.644407600000001</v>
+        <v>-2.908559999999999</v>
       </c>
       <c r="Q26">
-        <v>-1.771407600000001</v>
+        <v>-2.035559999999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09629076992898185</v>
+        <v>0.09696398019470161</v>
       </c>
       <c r="T26">
-        <v>0.7347022235987382</v>
+        <v>0.7444982532467214</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1457196205675209</v>
+        <v>0.1398908357448201</v>
       </c>
       <c r="W26">
-        <v>0.1715395001900418</v>
+        <v>0.1727099201824401</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5828784822700834</v>
+        <v>0.5595633429792801</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1159004651916362</v>
+        <v>0.1174504651916363</v>
       </c>
       <c r="C27">
-        <v>64.79469472163966</v>
+        <v>61.1511846332342</v>
       </c>
       <c r="D27">
-        <v>87.34469472163966</v>
+        <v>85.4551846332342</v>
       </c>
       <c r="E27">
-        <v>0.5499999999999972</v>
+        <v>2.303999999999995</v>
       </c>
       <c r="F27">
-        <v>43.84999999999999</v>
+        <v>45.60399999999999</v>
       </c>
       <c r="G27">
         <v>21.3</v>
@@ -3501,37 +3501,37 @@
         <v>4.927</v>
       </c>
       <c r="M27">
-        <v>8.805079999999998</v>
+        <v>9.157283199999998</v>
       </c>
       <c r="N27">
-        <v>-3.878079999999999</v>
+        <v>-4.230283199999999</v>
       </c>
       <c r="O27">
-        <v>-0.9695199999999997</v>
+        <v>-1.0575708</v>
       </c>
       <c r="P27">
-        <v>-2.908559999999999</v>
+        <v>-3.172712399999999</v>
       </c>
       <c r="Q27">
-        <v>-2.035559999999999</v>
+        <v>-2.299712399999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09696398019470161</v>
+        <v>0.09765538533246784</v>
       </c>
       <c r="T27">
-        <v>0.7444982532467214</v>
+        <v>0.7545590404527581</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1398908357448201</v>
+        <v>0.1345104189854039</v>
       </c>
       <c r="W27">
-        <v>0.1727099201824401</v>
+        <v>0.1737903078677309</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.5595633429792801</v>
+        <v>0.5380416759416156</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1174504651916363</v>
+        <v>0.1190004651916362</v>
       </c>
       <c r="C28">
-        <v>61.1511846332342</v>
+        <v>57.58769427228159</v>
       </c>
       <c r="D28">
-        <v>85.4551846332342</v>
+        <v>83.64569427228159</v>
       </c>
       <c r="E28">
-        <v>2.303999999999995</v>
+        <v>4.058</v>
       </c>
       <c r="F28">
-        <v>45.60399999999999</v>
+        <v>47.358</v>
       </c>
       <c r="G28">
         <v>21.3</v>
@@ -3583,37 +3583,37 @@
         <v>4.927</v>
       </c>
       <c r="M28">
-        <v>9.157283199999998</v>
+        <v>9.5094864</v>
       </c>
       <c r="N28">
-        <v>-4.230283199999999</v>
+        <v>-4.582486400000001</v>
       </c>
       <c r="O28">
-        <v>-1.0575708</v>
+        <v>-1.1456216</v>
       </c>
       <c r="P28">
-        <v>-3.172712399999999</v>
+        <v>-3.4368648</v>
       </c>
       <c r="Q28">
-        <v>-2.299712399999999</v>
+        <v>-2.5638648</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09765538533246784</v>
+        <v>0.09836573307674823</v>
       </c>
       <c r="T28">
-        <v>0.7545590404527581</v>
+        <v>0.7648954656644398</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.1345104189854039</v>
+        <v>0.1295285516155741</v>
       </c>
       <c r="W28">
-        <v>0.1737903078677309</v>
+        <v>0.1747906668355927</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.5380416759416156</v>
+        <v>0.5181142064622963</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1190004651916362</v>
+        <v>0.1305568793614347</v>
       </c>
       <c r="C29">
-        <v>57.58769427228159</v>
+        <v>44.42878774653872</v>
       </c>
       <c r="D29">
-        <v>83.64569427228159</v>
+        <v>72.24078774653871</v>
       </c>
       <c r="E29">
-        <v>4.058</v>
+        <v>5.811999999999998</v>
       </c>
       <c r="F29">
-        <v>47.358</v>
+        <v>49.11199999999999</v>
       </c>
       <c r="G29">
         <v>21.3</v>
@@ -3665,45 +3665,45 @@
         <v>4.927</v>
       </c>
       <c r="M29">
-        <v>9.5094864</v>
+        <v>11.5806096</v>
       </c>
       <c r="N29">
-        <v>-4.582486400000001</v>
+        <v>-6.653609599999999</v>
       </c>
       <c r="O29">
-        <v>-1.1456216</v>
+        <v>-1.6634024</v>
       </c>
       <c r="P29">
-        <v>-3.4368648</v>
+        <v>-4.9902072</v>
       </c>
       <c r="Q29">
-        <v>-2.5638648</v>
+        <v>-4.117207199999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09836573307674823</v>
+        <v>0.09938249904975655</v>
       </c>
       <c r="T29">
-        <v>0.7648954656644398</v>
+        <v>0.7796906494633692</v>
       </c>
       <c r="U29">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.1295285516155741</v>
+        <v>0.1063631399853079</v>
       </c>
       <c r="W29">
-        <v>0.1747906668355927</v>
+        <v>0.2107195715914644</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y29">
-        <v>0.5181142064622963</v>
+        <v>0.4254525599412314</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1305568793614347</v>
+        <v>0.1324568793614347</v>
       </c>
       <c r="C30">
-        <v>44.42878774653872</v>
+        <v>41.09086852708539</v>
       </c>
       <c r="D30">
-        <v>72.24078774653871</v>
+        <v>70.65686852708539</v>
       </c>
       <c r="E30">
-        <v>5.811999999999998</v>
+        <v>7.566000000000003</v>
       </c>
       <c r="F30">
-        <v>49.11199999999999</v>
+        <v>50.866</v>
       </c>
       <c r="G30">
         <v>21.3</v>
@@ -3747,37 +3747,37 @@
         <v>4.927</v>
       </c>
       <c r="M30">
-        <v>11.5806096</v>
+        <v>11.9942028</v>
       </c>
       <c r="N30">
-        <v>-6.653609599999999</v>
+        <v>-7.0672028</v>
       </c>
       <c r="O30">
-        <v>-1.6634024</v>
+        <v>-1.7668007</v>
       </c>
       <c r="P30">
-        <v>-4.9902072</v>
+        <v>-5.3004021</v>
       </c>
       <c r="Q30">
-        <v>-4.117207199999999</v>
+        <v>-4.4274021</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09938249904975655</v>
+        <v>0.1001371821349644</v>
       </c>
       <c r="T30">
-        <v>0.7796906494633692</v>
+        <v>0.7906722079065152</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.1063631399853079</v>
+        <v>0.1026954455030559</v>
       </c>
       <c r="W30">
-        <v>0.2107195715914644</v>
+        <v>0.2115844139503794</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.4254525599412314</v>
+        <v>0.4107817820122234</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1324568793614347</v>
+        <v>0.1343568793614348</v>
       </c>
       <c r="C31">
-        <v>41.0908685270854</v>
+        <v>37.82091571608419</v>
       </c>
       <c r="D31">
-        <v>70.65686852708539</v>
+        <v>69.14091571608418</v>
       </c>
       <c r="E31">
-        <v>7.565999999999995</v>
+        <v>9.319999999999993</v>
       </c>
       <c r="F31">
-        <v>50.86599999999999</v>
+        <v>52.61999999999999</v>
       </c>
       <c r="G31">
         <v>21.3</v>
@@ -3829,37 +3829,37 @@
         <v>4.927</v>
       </c>
       <c r="M31">
-        <v>11.9942028</v>
+        <v>12.407796</v>
       </c>
       <c r="N31">
-        <v>-7.067202799999999</v>
+        <v>-7.480795999999998</v>
       </c>
       <c r="O31">
-        <v>-1.7668007</v>
+        <v>-1.870199</v>
       </c>
       <c r="P31">
-        <v>-5.300402099999999</v>
+        <v>-5.610596999999999</v>
       </c>
       <c r="Q31">
-        <v>-4.427402099999999</v>
+        <v>-4.737596999999998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1001371821349644</v>
+        <v>0.1009134275940353</v>
       </c>
       <c r="T31">
-        <v>0.7906722079065152</v>
+        <v>0.8019675251623226</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.1026954455030559</v>
+        <v>0.09927226398628734</v>
       </c>
       <c r="W31">
-        <v>0.2115844139503794</v>
+        <v>0.2123916001520335</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.4107817820122235</v>
+        <v>0.3970890559451493</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1343568793614348</v>
+        <v>0.1362568793614348</v>
       </c>
       <c r="C32">
-        <v>37.82091571608419</v>
+        <v>34.61464651568805</v>
       </c>
       <c r="D32">
-        <v>69.14091571608418</v>
+        <v>67.68864651568805</v>
       </c>
       <c r="E32">
-        <v>9.319999999999993</v>
+        <v>11.074</v>
       </c>
       <c r="F32">
-        <v>52.61999999999999</v>
+        <v>54.374</v>
       </c>
       <c r="G32">
         <v>21.3</v>
@@ -3911,37 +3911,37 @@
         <v>4.927</v>
       </c>
       <c r="M32">
-        <v>12.407796</v>
+        <v>12.8213892</v>
       </c>
       <c r="N32">
-        <v>-7.480795999999998</v>
+        <v>-7.894389199999999</v>
       </c>
       <c r="O32">
-        <v>-1.870199</v>
+        <v>-1.9735973</v>
       </c>
       <c r="P32">
-        <v>-5.610596999999999</v>
+        <v>-5.920791899999999</v>
       </c>
       <c r="Q32">
-        <v>-4.737596999999998</v>
+        <v>-5.047791899999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1009134275940353</v>
+        <v>0.1017121729214851</v>
       </c>
       <c r="T32">
-        <v>0.8019675251623226</v>
+        <v>0.8135902429182984</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.09927226398628734</v>
+        <v>0.09606993288995548</v>
       </c>
       <c r="W32">
-        <v>0.2123916001520335</v>
+        <v>0.2131467098245485</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3970890559451493</v>
+        <v>0.384279731559822</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1362568793614348</v>
+        <v>0.1381568793614347</v>
       </c>
       <c r="C33">
-        <v>34.61464651568805</v>
+        <v>31.46813055727741</v>
       </c>
       <c r="D33">
-        <v>67.68864651568805</v>
+        <v>66.29613055727741</v>
       </c>
       <c r="E33">
-        <v>11.074</v>
+        <v>12.828</v>
       </c>
       <c r="F33">
-        <v>54.374</v>
+        <v>56.12799999999999</v>
       </c>
       <c r="G33">
         <v>21.3</v>
@@ -3993,37 +3993,37 @@
         <v>4.927</v>
       </c>
       <c r="M33">
-        <v>12.8213892</v>
+        <v>13.2349824</v>
       </c>
       <c r="N33">
-        <v>-7.894389199999999</v>
+        <v>-8.307982399999998</v>
       </c>
       <c r="O33">
-        <v>-1.9735973</v>
+        <v>-2.0769956</v>
       </c>
       <c r="P33">
-        <v>-5.920791899999999</v>
+        <v>-6.230986799999998</v>
       </c>
       <c r="Q33">
-        <v>-5.047791899999999</v>
+        <v>-5.357986799999998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1017121729214851</v>
+        <v>0.1025344107585658</v>
       </c>
       <c r="T33">
-        <v>0.8135902429182984</v>
+        <v>0.8255548053141556</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.09606993288995548</v>
+        <v>0.09306774748714437</v>
       </c>
       <c r="W33">
-        <v>0.2131467098245485</v>
+        <v>0.2138546251425314</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.384279731559822</v>
+        <v>0.3722709899485775</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1381568793614347</v>
+        <v>0.1400568793614348</v>
       </c>
       <c r="C34">
-        <v>31.46813055727741</v>
+        <v>28.3777543806822</v>
       </c>
       <c r="D34">
-        <v>66.29613055727741</v>
+        <v>64.9597543806822</v>
       </c>
       <c r="E34">
-        <v>12.828</v>
+        <v>14.582</v>
       </c>
       <c r="F34">
-        <v>56.12799999999999</v>
+        <v>57.882</v>
       </c>
       <c r="G34">
         <v>21.3</v>
@@ -4075,37 +4075,37 @@
         <v>4.927</v>
       </c>
       <c r="M34">
-        <v>13.2349824</v>
+        <v>13.6485756</v>
       </c>
       <c r="N34">
-        <v>-8.307982399999998</v>
+        <v>-8.721575600000001</v>
       </c>
       <c r="O34">
-        <v>-2.0769956</v>
+        <v>-2.1803939</v>
       </c>
       <c r="P34">
-        <v>-6.230986799999998</v>
+        <v>-6.541181700000001</v>
       </c>
       <c r="Q34">
-        <v>-5.357986799999998</v>
+        <v>-5.668181700000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1025344107585658</v>
+        <v>0.1033811930086936</v>
       </c>
       <c r="T34">
-        <v>0.8255548053141556</v>
+        <v>0.8378765188263072</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.09306774748714437</v>
+        <v>0.09024751271480665</v>
       </c>
       <c r="W34">
-        <v>0.2138546251425314</v>
+        <v>0.2145196365018486</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3722709899485775</v>
+        <v>0.3609900508592266</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1400568793614348</v>
+        <v>0.1419568793614348</v>
       </c>
       <c r="C35">
-        <v>28.3777543806822</v>
+        <v>25.34019012461508</v>
       </c>
       <c r="D35">
-        <v>64.9597543806822</v>
+        <v>63.67619012461508</v>
       </c>
       <c r="E35">
-        <v>14.582</v>
+        <v>16.336</v>
       </c>
       <c r="F35">
-        <v>57.882</v>
+        <v>59.636</v>
       </c>
       <c r="G35">
         <v>21.3</v>
@@ -4157,37 +4157,37 @@
         <v>4.927</v>
       </c>
       <c r="M35">
-        <v>13.6485756</v>
+        <v>14.0621688</v>
       </c>
       <c r="N35">
-        <v>-8.721575600000001</v>
+        <v>-9.135168800000001</v>
       </c>
       <c r="O35">
-        <v>-2.1803939</v>
+        <v>-2.2837922</v>
       </c>
       <c r="P35">
-        <v>-6.541181700000001</v>
+        <v>-6.8513766</v>
       </c>
       <c r="Q35">
-        <v>-5.668181700000001</v>
+        <v>-5.9783766</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1033811930086936</v>
+        <v>0.1042536353270071</v>
       </c>
       <c r="T35">
-        <v>0.8378765188263072</v>
+        <v>0.8505716175964028</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.09024751271480665</v>
+        <v>0.08759317410554764</v>
       </c>
       <c r="W35">
-        <v>0.2145196365018486</v>
+        <v>0.2151455295459119</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3609900508592266</v>
+        <v>0.3503726964221906</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1419568793614348</v>
+        <v>0.1438568793614348</v>
       </c>
       <c r="C36">
-        <v>25.34019012461508</v>
+        <v>22.35236785712455</v>
       </c>
       <c r="D36">
-        <v>63.67619012461508</v>
+        <v>62.44236785712455</v>
       </c>
       <c r="E36">
-        <v>16.336</v>
+        <v>18.09</v>
       </c>
       <c r="F36">
-        <v>59.636</v>
+        <v>61.39</v>
       </c>
       <c r="G36">
         <v>21.3</v>
@@ -4239,37 +4239,37 @@
         <v>4.927</v>
       </c>
       <c r="M36">
-        <v>14.0621688</v>
+        <v>14.475762</v>
       </c>
       <c r="N36">
-        <v>-9.135168800000001</v>
+        <v>-9.548762000000002</v>
       </c>
       <c r="O36">
-        <v>-2.2837922</v>
+        <v>-2.3871905</v>
       </c>
       <c r="P36">
-        <v>-6.8513766</v>
+        <v>-7.161571500000001</v>
       </c>
       <c r="Q36">
-        <v>-5.9783766</v>
+        <v>-6.288571500000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1042536353270071</v>
+        <v>0.1051529220243457</v>
       </c>
       <c r="T36">
-        <v>0.8505716175964028</v>
+        <v>0.8636573347901937</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.08759317410554764</v>
+        <v>0.08509051198824627</v>
       </c>
       <c r="W36">
-        <v>0.2151455295459119</v>
+        <v>0.2157356572731715</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3503726964221906</v>
+        <v>0.3403620479529851</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1438568793614348</v>
+        <v>0.1457568793614347</v>
       </c>
       <c r="C37">
-        <v>22.35236785712455</v>
+        <v>19.41145106173779</v>
       </c>
       <c r="D37">
-        <v>62.44236785712455</v>
+        <v>61.25545106173779</v>
       </c>
       <c r="E37">
-        <v>18.09</v>
+        <v>19.844</v>
       </c>
       <c r="F37">
-        <v>61.39</v>
+        <v>63.144</v>
       </c>
       <c r="G37">
         <v>21.3</v>
@@ -4321,37 +4321,37 @@
         <v>4.927</v>
       </c>
       <c r="M37">
-        <v>14.475762</v>
+        <v>14.8893552</v>
       </c>
       <c r="N37">
-        <v>-9.548762000000002</v>
+        <v>-9.962355200000001</v>
       </c>
       <c r="O37">
-        <v>-2.3871905</v>
+        <v>-2.4905888</v>
       </c>
       <c r="P37">
-        <v>-7.161571500000001</v>
+        <v>-7.471766400000001</v>
       </c>
       <c r="Q37">
-        <v>-6.288571500000001</v>
+        <v>-6.598766400000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1051529220243457</v>
+        <v>0.1060803114309761</v>
       </c>
       <c r="T37">
-        <v>0.8636573347901937</v>
+        <v>0.8771519806462904</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.08509051198824627</v>
+        <v>0.08272688665523943</v>
       </c>
       <c r="W37">
-        <v>0.2157356572731715</v>
+        <v>0.2162930001266946</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3403620479529851</v>
+        <v>0.3309075466209578</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1457568793614347</v>
+        <v>0.1476568793614348</v>
       </c>
       <c r="C38">
-        <v>19.41145106173779</v>
+        <v>16.51481486723675</v>
       </c>
       <c r="D38">
-        <v>61.25545106173779</v>
+        <v>60.11281486723674</v>
       </c>
       <c r="E38">
-        <v>19.84399999999999</v>
+        <v>21.598</v>
       </c>
       <c r="F38">
-        <v>63.14399999999999</v>
+        <v>64.898</v>
       </c>
       <c r="G38">
         <v>21.3</v>
@@ -4403,37 +4403,37 @@
         <v>4.927</v>
       </c>
       <c r="M38">
-        <v>14.8893552</v>
+        <v>15.3029484</v>
       </c>
       <c r="N38">
-        <v>-9.962355199999999</v>
+        <v>-10.3759484</v>
       </c>
       <c r="O38">
-        <v>-2.4905888</v>
+        <v>-2.5939871</v>
       </c>
       <c r="P38">
-        <v>-7.4717664</v>
+        <v>-7.781961300000001</v>
       </c>
       <c r="Q38">
-        <v>-6.5987664</v>
+        <v>-6.908961300000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1060803114309761</v>
+        <v>0.1070371417711503</v>
       </c>
       <c r="T38">
-        <v>0.8771519806462902</v>
+        <v>0.8910750279581362</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.08272688665523945</v>
+        <v>0.08049102485374648</v>
       </c>
       <c r="W38">
-        <v>0.2162930001266946</v>
+        <v>0.2168202163394866</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3309075466209578</v>
+        <v>0.3219640994149859</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1476568793614348</v>
+        <v>0.1495568793614347</v>
       </c>
       <c r="C39">
-        <v>16.51481486723675</v>
+        <v>13.66002666937774</v>
       </c>
       <c r="D39">
-        <v>60.11281486723674</v>
+        <v>59.01202666937773</v>
       </c>
       <c r="E39">
-        <v>21.598</v>
+        <v>23.35199999999999</v>
       </c>
       <c r="F39">
-        <v>64.898</v>
+        <v>66.65199999999999</v>
       </c>
       <c r="G39">
         <v>21.3</v>
@@ -4485,37 +4485,37 @@
         <v>4.927</v>
       </c>
       <c r="M39">
-        <v>15.3029484</v>
+        <v>15.7165416</v>
       </c>
       <c r="N39">
-        <v>-10.3759484</v>
+        <v>-10.7895416</v>
       </c>
       <c r="O39">
-        <v>-2.5939871</v>
+        <v>-2.697385399999999</v>
       </c>
       <c r="P39">
-        <v>-7.781961300000001</v>
+        <v>-8.092156199999998</v>
       </c>
       <c r="Q39">
-        <v>-6.908961300000001</v>
+        <v>-7.219156199999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1070371417711503</v>
+        <v>0.1080248376061689</v>
       </c>
       <c r="T39">
-        <v>0.8910750279581362</v>
+        <v>0.9054472058284286</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.08049102485374648</v>
+        <v>0.07837283998917421</v>
       </c>
       <c r="W39">
-        <v>0.2168202163394866</v>
+        <v>0.2173196843305527</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3219640994149859</v>
+        <v>0.3134913599566969</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1495568793614347</v>
+        <v>0.1514568793614348</v>
       </c>
       <c r="C40">
-        <v>13.66002666937774</v>
+        <v>10.84482884345799</v>
       </c>
       <c r="D40">
-        <v>59.01202666937773</v>
+        <v>57.95082884345798</v>
       </c>
       <c r="E40">
-        <v>23.35199999999999</v>
+        <v>25.10599999999999</v>
       </c>
       <c r="F40">
-        <v>66.65199999999999</v>
+        <v>68.40599999999999</v>
       </c>
       <c r="G40">
         <v>21.3</v>
@@ -4567,37 +4567,37 @@
         <v>4.927</v>
       </c>
       <c r="M40">
-        <v>15.7165416</v>
+        <v>16.1301348</v>
       </c>
       <c r="N40">
-        <v>-10.7895416</v>
+        <v>-11.2031348</v>
       </c>
       <c r="O40">
-        <v>-2.697385399999999</v>
+        <v>-2.8007837</v>
       </c>
       <c r="P40">
-        <v>-8.092156199999998</v>
+        <v>-8.402351100000001</v>
       </c>
       <c r="Q40">
-        <v>-7.219156199999998</v>
+        <v>-7.5293511</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1080248376061689</v>
+        <v>0.1090449169111881</v>
       </c>
       <c r="T40">
-        <v>0.9054472058284286</v>
+        <v>0.9202906026452883</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.07837283998917421</v>
+        <v>0.07636327998945179</v>
       </c>
       <c r="W40">
-        <v>0.2173196843305527</v>
+        <v>0.2177935385784873</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3134913599566969</v>
+        <v>0.3054531199578071</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1514568793614348</v>
+        <v>0.1533568793614348</v>
       </c>
       <c r="C41">
-        <v>10.84482884345799</v>
+        <v>8.067123289185005</v>
       </c>
       <c r="D41">
-        <v>57.95082884345798</v>
+        <v>56.927123289185</v>
       </c>
       <c r="E41">
-        <v>25.10599999999999</v>
+        <v>26.86</v>
       </c>
       <c r="F41">
-        <v>68.40599999999999</v>
+        <v>70.16</v>
       </c>
       <c r="G41">
         <v>21.3</v>
@@ -4649,37 +4649,37 @@
         <v>4.927</v>
       </c>
       <c r="M41">
-        <v>16.1301348</v>
+        <v>16.543728</v>
       </c>
       <c r="N41">
-        <v>-11.2031348</v>
+        <v>-11.616728</v>
       </c>
       <c r="O41">
-        <v>-2.8007837</v>
+        <v>-2.904182</v>
       </c>
       <c r="P41">
-        <v>-8.402351100000001</v>
+        <v>-8.712546000000001</v>
       </c>
       <c r="Q41">
-        <v>-7.5293511</v>
+        <v>-7.839546000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1090449169111881</v>
+        <v>0.1100989988597079</v>
       </c>
       <c r="T41">
-        <v>0.9202906026452883</v>
+        <v>0.9356287793560429</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.07636327998945179</v>
+        <v>0.07445419798971549</v>
       </c>
       <c r="W41">
-        <v>0.2177935385784873</v>
+        <v>0.2182437001140251</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3054531199578071</v>
+        <v>0.2978167919588619</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1533568793614348</v>
+        <v>0.1552568793614348</v>
       </c>
       <c r="C42">
-        <v>8.067123289185005</v>
+        <v>5.324957585206789</v>
       </c>
       <c r="D42">
-        <v>56.927123289185</v>
+        <v>55.93895758520679</v>
       </c>
       <c r="E42">
-        <v>26.86</v>
+        <v>28.614</v>
       </c>
       <c r="F42">
-        <v>70.16</v>
+        <v>71.914</v>
       </c>
       <c r="G42">
         <v>21.3</v>
@@ -4731,37 +4731,37 @@
         <v>4.927</v>
       </c>
       <c r="M42">
-        <v>16.543728</v>
+        <v>16.9573212</v>
       </c>
       <c r="N42">
-        <v>-11.616728</v>
+        <v>-12.0303212</v>
       </c>
       <c r="O42">
-        <v>-2.904182</v>
+        <v>-3.007580300000001</v>
       </c>
       <c r="P42">
-        <v>-8.712546000000001</v>
+        <v>-9.022740900000002</v>
       </c>
       <c r="Q42">
-        <v>-7.839546000000001</v>
+        <v>-8.149740900000003</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1100989988597079</v>
+        <v>0.1111888123997029</v>
       </c>
       <c r="T42">
-        <v>0.9356287793560429</v>
+        <v>0.9514868942603827</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.07445419798971549</v>
+        <v>0.07263824194118583</v>
       </c>
       <c r="W42">
-        <v>0.2182437001140251</v>
+        <v>0.2186719025502684</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2978167919588619</v>
+        <v>0.2905529677647434</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1552568793614348</v>
+        <v>0.1571568793614347</v>
       </c>
       <c r="C43">
-        <v>5.324957585206789</v>
+        <v>2.616512561052318</v>
       </c>
       <c r="D43">
-        <v>55.93895758520679</v>
+        <v>54.98451256105231</v>
       </c>
       <c r="E43">
-        <v>28.614</v>
+        <v>30.36799999999999</v>
       </c>
       <c r="F43">
-        <v>71.914</v>
+        <v>73.66799999999999</v>
       </c>
       <c r="G43">
         <v>21.3</v>
@@ -4813,37 +4813,37 @@
         <v>4.927</v>
       </c>
       <c r="M43">
-        <v>16.9573212</v>
+        <v>17.3709144</v>
       </c>
       <c r="N43">
-        <v>-12.0303212</v>
+        <v>-12.4439144</v>
       </c>
       <c r="O43">
-        <v>-3.007580300000001</v>
+        <v>-3.1109786</v>
       </c>
       <c r="P43">
-        <v>-9.022740900000002</v>
+        <v>-9.332935800000001</v>
       </c>
       <c r="Q43">
-        <v>-8.149740900000003</v>
+        <v>-8.459935800000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1111888123997029</v>
+        <v>0.1123162057169391</v>
       </c>
       <c r="T43">
-        <v>0.9514868942603827</v>
+        <v>0.9678918407131479</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07263824194118583</v>
+        <v>0.07090875999020523</v>
       </c>
       <c r="W43">
-        <v>0.2186719025502684</v>
+        <v>0.2190797143943096</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2905529677647434</v>
+        <v>0.283635039960821</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1571568793614347</v>
+        <v>0.1590568793614348</v>
       </c>
       <c r="C44">
-        <v>2.616512561052318</v>
+        <v>-0.05990887996765082</v>
       </c>
       <c r="D44">
-        <v>54.98451256105231</v>
+        <v>54.06209112003233</v>
       </c>
       <c r="E44">
-        <v>30.36799999999999</v>
+        <v>32.12199999999999</v>
       </c>
       <c r="F44">
-        <v>73.66799999999999</v>
+        <v>75.42199999999998</v>
       </c>
       <c r="G44">
         <v>21.3</v>
@@ -4895,37 +4895,37 @@
         <v>4.927</v>
       </c>
       <c r="M44">
-        <v>17.3709144</v>
+        <v>17.7845076</v>
       </c>
       <c r="N44">
-        <v>-12.4439144</v>
+        <v>-12.8575076</v>
       </c>
       <c r="O44">
-        <v>-3.1109786</v>
+        <v>-3.2143769</v>
       </c>
       <c r="P44">
-        <v>-9.332935800000001</v>
+        <v>-9.643130699999999</v>
       </c>
       <c r="Q44">
-        <v>-8.459935800000002</v>
+        <v>-8.770130699999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1123162057169391</v>
+        <v>0.1134831566944293</v>
       </c>
       <c r="T44">
-        <v>0.9678918407131479</v>
+        <v>0.9848723993221505</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.07090875999020523</v>
+        <v>0.06925971906020047</v>
       </c>
       <c r="W44">
-        <v>0.2190797143943096</v>
+        <v>0.2194685582456047</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.283635039960821</v>
+        <v>0.2770388762408018</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1590568793614348</v>
+        <v>0.1609568793614348</v>
       </c>
       <c r="C45">
-        <v>-0.05990887996765082</v>
+        <v>-2.705891831378381</v>
       </c>
       <c r="D45">
-        <v>54.06209112003233</v>
+        <v>53.1701081686216</v>
       </c>
       <c r="E45">
-        <v>32.12199999999999</v>
+        <v>33.87599999999999</v>
       </c>
       <c r="F45">
-        <v>75.42199999999998</v>
+        <v>77.17599999999999</v>
       </c>
       <c r="G45">
         <v>21.3</v>
@@ -4977,37 +4977,37 @@
         <v>4.927</v>
       </c>
       <c r="M45">
-        <v>17.7845076</v>
+        <v>18.1981008</v>
       </c>
       <c r="N45">
-        <v>-12.8575076</v>
+        <v>-13.2711008</v>
       </c>
       <c r="O45">
-        <v>-3.2143769</v>
+        <v>-3.3177752</v>
       </c>
       <c r="P45">
-        <v>-9.643130699999999</v>
+        <v>-9.953325599999999</v>
       </c>
       <c r="Q45">
-        <v>-8.770130699999999</v>
+        <v>-9.0803256</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1134831566944293</v>
+        <v>0.1146917844925441</v>
       </c>
       <c r="T45">
-        <v>0.9848723993221505</v>
+        <v>1.002459406452903</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06925971906020047</v>
+        <v>0.067685634536105</v>
       </c>
       <c r="W45">
-        <v>0.2194685582456047</v>
+        <v>0.2198397273763865</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2770388762408018</v>
+        <v>0.27074253814442</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1609568793614348</v>
+        <v>0.1628568793614348</v>
       </c>
       <c r="C46">
-        <v>-2.705891831378381</v>
+        <v>-5.322918473396186</v>
       </c>
       <c r="D46">
-        <v>53.1701081686216</v>
+        <v>52.3070815266038</v>
       </c>
       <c r="E46">
-        <v>33.87599999999999</v>
+        <v>35.63</v>
       </c>
       <c r="F46">
-        <v>77.17599999999999</v>
+        <v>78.92999999999999</v>
       </c>
       <c r="G46">
         <v>21.3</v>
@@ -5059,37 +5059,37 @@
         <v>4.927</v>
       </c>
       <c r="M46">
-        <v>18.1981008</v>
+        <v>18.611694</v>
       </c>
       <c r="N46">
-        <v>-13.2711008</v>
+        <v>-13.684694</v>
       </c>
       <c r="O46">
-        <v>-3.3177752</v>
+        <v>-3.4211735</v>
       </c>
       <c r="P46">
-        <v>-9.953325599999999</v>
+        <v>-10.2635205</v>
       </c>
       <c r="Q46">
-        <v>-9.0803256</v>
+        <v>-9.390520500000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1146917844925441</v>
+        <v>0.1159443623924086</v>
       </c>
       <c r="T46">
-        <v>1.002459406452903</v>
+        <v>1.020685941115683</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.067685634536105</v>
+        <v>0.06618150932419155</v>
       </c>
       <c r="W46">
-        <v>0.2198397273763865</v>
+        <v>0.2201944001013557</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.27074253814442</v>
+        <v>0.2647260372967662</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1628568793614348</v>
+        <v>0.1647568793614348</v>
       </c>
       <c r="C47">
-        <v>-5.322918473396186</v>
+        <v>-7.912376291674917</v>
       </c>
       <c r="D47">
-        <v>52.3070815266038</v>
+        <v>51.47162370832508</v>
       </c>
       <c r="E47">
-        <v>35.63</v>
+        <v>37.384</v>
       </c>
       <c r="F47">
-        <v>78.92999999999999</v>
+        <v>80.684</v>
       </c>
       <c r="G47">
         <v>21.3</v>
@@ -5141,37 +5141,37 @@
         <v>4.927</v>
       </c>
       <c r="M47">
-        <v>18.611694</v>
+        <v>19.0252872</v>
       </c>
       <c r="N47">
-        <v>-13.684694</v>
+        <v>-14.0982872</v>
       </c>
       <c r="O47">
-        <v>-3.4211735</v>
+        <v>-3.5245718</v>
       </c>
       <c r="P47">
-        <v>-10.2635205</v>
+        <v>-10.5737154</v>
       </c>
       <c r="Q47">
-        <v>-9.390520500000001</v>
+        <v>-9.700715400000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1159443623924086</v>
+        <v>0.1172433320663421</v>
       </c>
       <c r="T47">
-        <v>1.020685941115683</v>
+        <v>1.039587532617826</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06618150932419155</v>
+        <v>0.06474278086062216</v>
       </c>
       <c r="W47">
-        <v>0.2201944001013557</v>
+        <v>0.2205336522730653</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2647260372967662</v>
+        <v>0.2589711234424886</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1647568793614348</v>
+        <v>0.1666568793614348</v>
       </c>
       <c r="C48">
-        <v>-7.912376291674917</v>
+        <v>-10.47556552080721</v>
       </c>
       <c r="D48">
-        <v>51.47162370832508</v>
+        <v>50.66243447919278</v>
       </c>
       <c r="E48">
-        <v>37.384</v>
+        <v>39.13799999999999</v>
       </c>
       <c r="F48">
-        <v>80.684</v>
+        <v>82.43799999999999</v>
       </c>
       <c r="G48">
         <v>21.3</v>
@@ -5223,37 +5223,37 @@
         <v>4.927</v>
       </c>
       <c r="M48">
-        <v>19.0252872</v>
+        <v>19.4388804</v>
       </c>
       <c r="N48">
-        <v>-14.0982872</v>
+        <v>-14.5118804</v>
       </c>
       <c r="O48">
-        <v>-3.5245718</v>
+        <v>-3.6279701</v>
       </c>
       <c r="P48">
-        <v>-10.5737154</v>
+        <v>-10.8839103</v>
       </c>
       <c r="Q48">
-        <v>-9.700715400000002</v>
+        <v>-10.0109103</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1172433320663421</v>
+        <v>0.1185913194638202</v>
       </c>
       <c r="T48">
-        <v>1.039587532617826</v>
+        <v>1.059202391723822</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06474278086062216</v>
+        <v>0.06336527488486425</v>
       </c>
       <c r="W48">
-        <v>0.2205336522730653</v>
+        <v>0.220858468182149</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2589711234424886</v>
+        <v>0.2534610995394571</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1666568793614348</v>
+        <v>0.1685568793614348</v>
       </c>
       <c r="C49">
-        <v>-10.47556552080721</v>
+        <v>-13.01370589657428</v>
       </c>
       <c r="D49">
-        <v>50.66243447919278</v>
+        <v>49.87829410342572</v>
       </c>
       <c r="E49">
-        <v>39.13799999999999</v>
+        <v>40.892</v>
       </c>
       <c r="F49">
-        <v>82.43799999999999</v>
+        <v>84.19199999999999</v>
       </c>
       <c r="G49">
         <v>21.3</v>
@@ -5305,37 +5305,37 @@
         <v>4.927</v>
       </c>
       <c r="M49">
-        <v>19.4388804</v>
+        <v>19.8524736</v>
       </c>
       <c r="N49">
-        <v>-14.5118804</v>
+        <v>-14.9254736</v>
       </c>
       <c r="O49">
-        <v>-3.6279701</v>
+        <v>-3.7313684</v>
       </c>
       <c r="P49">
-        <v>-10.8839103</v>
+        <v>-11.1941052</v>
       </c>
       <c r="Q49">
-        <v>-10.0109103</v>
+        <v>-10.3211052</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1185913194638202</v>
+        <v>0.1199911525304321</v>
       </c>
       <c r="T49">
-        <v>1.059202391723822</v>
+        <v>1.079571668487742</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06336527488486425</v>
+        <v>0.06204516499142958</v>
       </c>
       <c r="W49">
-        <v>0.220858468182149</v>
+        <v>0.2211697500950209</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2534610995394571</v>
+        <v>0.2481806599657184</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1685568793614348</v>
+        <v>0.1704568793614348</v>
       </c>
       <c r="C50">
-        <v>-13.01370589657428</v>
+        <v>-15.52794279069489</v>
       </c>
       <c r="D50">
-        <v>49.87829410342572</v>
+        <v>49.11805720930509</v>
       </c>
       <c r="E50">
-        <v>40.892</v>
+        <v>42.64599999999999</v>
       </c>
       <c r="F50">
-        <v>84.19199999999999</v>
+        <v>85.94599999999998</v>
       </c>
       <c r="G50">
         <v>21.3</v>
@@ -5387,37 +5387,37 @@
         <v>4.927</v>
       </c>
       <c r="M50">
-        <v>19.8524736</v>
+        <v>20.2660668</v>
       </c>
       <c r="N50">
-        <v>-14.9254736</v>
+        <v>-15.3390668</v>
       </c>
       <c r="O50">
-        <v>-3.7313684</v>
+        <v>-3.834766699999999</v>
       </c>
       <c r="P50">
-        <v>-11.1941052</v>
+        <v>-11.5043001</v>
       </c>
       <c r="Q50">
-        <v>-10.3211052</v>
+        <v>-10.6313001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1199911525304321</v>
+        <v>0.121445881011421</v>
       </c>
       <c r="T50">
-        <v>1.079571668487742</v>
+        <v>1.100739740418874</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06204516499142958</v>
+        <v>0.06077893713446163</v>
       </c>
       <c r="W50">
-        <v>0.2211697500950209</v>
+        <v>0.221468326623694</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2481806599657184</v>
+        <v>0.2431157485378466</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1704568793614348</v>
+        <v>0.1723568793614347</v>
       </c>
       <c r="C51">
-        <v>-15.52794279069489</v>
+        <v>-18.01935279296869</v>
       </c>
       <c r="D51">
-        <v>49.11805720930509</v>
+        <v>48.3806472070313</v>
       </c>
       <c r="E51">
-        <v>42.64599999999999</v>
+        <v>44.39999999999999</v>
       </c>
       <c r="F51">
-        <v>85.94599999999998</v>
+        <v>87.69999999999999</v>
       </c>
       <c r="G51">
         <v>21.3</v>
@@ -5469,37 +5469,37 @@
         <v>4.927</v>
       </c>
       <c r="M51">
-        <v>20.2660668</v>
+        <v>20.67966</v>
       </c>
       <c r="N51">
-        <v>-15.3390668</v>
+        <v>-15.75266</v>
       </c>
       <c r="O51">
-        <v>-3.834766699999999</v>
+        <v>-3.938165</v>
       </c>
       <c r="P51">
-        <v>-11.5043001</v>
+        <v>-11.814495</v>
       </c>
       <c r="Q51">
-        <v>-10.6313001</v>
+        <v>-10.941495</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.121445881011421</v>
+        <v>0.1229587986316494</v>
       </c>
       <c r="T51">
-        <v>1.100739740418874</v>
+        <v>1.122754535227251</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06077893713446163</v>
+        <v>0.0595633583917724</v>
       </c>
       <c r="W51">
-        <v>0.221468326623694</v>
+        <v>0.2217549600912201</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2431157485378466</v>
+        <v>0.2382534335670896</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1723568793614347</v>
+        <v>0.1742568793614347</v>
       </c>
       <c r="C52">
-        <v>-18.01935279296869</v>
+        <v>-20.48894879802748</v>
       </c>
       <c r="D52">
-        <v>48.3806472070313</v>
+        <v>47.66505120197252</v>
       </c>
       <c r="E52">
-        <v>44.39999999999999</v>
+        <v>46.154</v>
       </c>
       <c r="F52">
-        <v>87.69999999999999</v>
+        <v>89.45399999999999</v>
       </c>
       <c r="G52">
         <v>21.3</v>
@@ -5551,37 +5551,37 @@
         <v>4.927</v>
       </c>
       <c r="M52">
-        <v>20.67966</v>
+        <v>21.0932532</v>
       </c>
       <c r="N52">
-        <v>-15.75266</v>
+        <v>-16.1662532</v>
       </c>
       <c r="O52">
-        <v>-3.938165</v>
+        <v>-4.0415633</v>
       </c>
       <c r="P52">
-        <v>-11.814495</v>
+        <v>-12.1246899</v>
       </c>
       <c r="Q52">
-        <v>-10.941495</v>
+        <v>-11.2516899</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1229587986316494</v>
+        <v>0.124533467991479</v>
       </c>
       <c r="T52">
-        <v>1.122754535227251</v>
+        <v>1.145667893089032</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0595633583917724</v>
+        <v>0.05839544940369842</v>
       </c>
       <c r="W52">
-        <v>0.2217549600912201</v>
+        <v>0.2220303530306079</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2382534335670896</v>
+        <v>0.2335817976147937</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1742568793614347</v>
+        <v>0.1761568793614348</v>
       </c>
       <c r="C53">
-        <v>-20.48894879802748</v>
+        <v>-22.93768464723912</v>
       </c>
       <c r="D53">
-        <v>47.66505120197252</v>
+        <v>46.97031535276086</v>
       </c>
       <c r="E53">
-        <v>46.154</v>
+        <v>47.90799999999999</v>
       </c>
       <c r="F53">
-        <v>89.45399999999999</v>
+        <v>91.20799999999998</v>
       </c>
       <c r="G53">
         <v>21.3</v>
@@ -5633,37 +5633,37 @@
         <v>4.927</v>
       </c>
       <c r="M53">
-        <v>21.0932532</v>
+        <v>21.5068464</v>
       </c>
       <c r="N53">
-        <v>-16.1662532</v>
+        <v>-16.5798464</v>
       </c>
       <c r="O53">
-        <v>-4.0415633</v>
+        <v>-4.144961599999999</v>
       </c>
       <c r="P53">
-        <v>-12.1246899</v>
+        <v>-12.4348848</v>
       </c>
       <c r="Q53">
-        <v>-11.2516899</v>
+        <v>-11.5618848</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.124533467991479</v>
+        <v>0.1261737485746348</v>
       </c>
       <c r="T53">
-        <v>1.145667893089032</v>
+        <v>1.169535974195054</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05839544940369842</v>
+        <v>0.05727245999208885</v>
       </c>
       <c r="W53">
-        <v>0.2220303530306079</v>
+        <v>0.2222951539338655</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2335817976147937</v>
+        <v>0.2290898399683554</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1761568793614348</v>
+        <v>0.1780568793614348</v>
       </c>
       <c r="C54">
-        <v>-22.93768464723912</v>
+        <v>-25.36645937049839</v>
       </c>
       <c r="D54">
-        <v>46.97031535276086</v>
+        <v>46.2955406295016</v>
       </c>
       <c r="E54">
-        <v>47.90799999999999</v>
+        <v>49.66199999999999</v>
       </c>
       <c r="F54">
-        <v>91.20799999999998</v>
+        <v>92.96199999999999</v>
       </c>
       <c r="G54">
         <v>21.3</v>
@@ -5715,37 +5715,37 @@
         <v>4.927</v>
       </c>
       <c r="M54">
-        <v>21.5068464</v>
+        <v>21.9204396</v>
       </c>
       <c r="N54">
-        <v>-16.5798464</v>
+        <v>-16.9934396</v>
       </c>
       <c r="O54">
-        <v>-4.144961599999999</v>
+        <v>-4.2483599</v>
       </c>
       <c r="P54">
-        <v>-12.4348848</v>
+        <v>-12.7450797</v>
       </c>
       <c r="Q54">
-        <v>-11.5618848</v>
+        <v>-11.8720797</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1261737485746348</v>
+        <v>0.127883828331542</v>
       </c>
       <c r="T54">
-        <v>1.169535974195054</v>
+        <v>1.194419718326864</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05727245999208885</v>
+        <v>0.05619184753940792</v>
       </c>
       <c r="W54">
-        <v>0.2222951539338655</v>
+        <v>0.2225499623502076</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2290898399683554</v>
+        <v>0.2247673901576317</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1780568793614348</v>
+        <v>0.1799568793614348</v>
       </c>
       <c r="C55">
-        <v>-25.36645937049839</v>
+        <v>-27.77612106757078</v>
       </c>
       <c r="D55">
-        <v>46.2955406295016</v>
+        <v>45.63987893242921</v>
       </c>
       <c r="E55">
-        <v>49.66199999999999</v>
+        <v>51.416</v>
       </c>
       <c r="F55">
-        <v>92.96199999999999</v>
+        <v>94.71599999999999</v>
       </c>
       <c r="G55">
         <v>21.3</v>
@@ -5797,37 +5797,37 @@
         <v>4.927</v>
       </c>
       <c r="M55">
-        <v>21.9204396</v>
+        <v>22.3340328</v>
       </c>
       <c r="N55">
-        <v>-16.9934396</v>
+        <v>-17.4070328</v>
       </c>
       <c r="O55">
-        <v>-4.2483599</v>
+        <v>-4.3517582</v>
       </c>
       <c r="P55">
-        <v>-12.7450797</v>
+        <v>-13.0552746</v>
       </c>
       <c r="Q55">
-        <v>-11.8720797</v>
+        <v>-12.1822746</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.127883828331542</v>
+        <v>0.1296682593822276</v>
       </c>
       <c r="T55">
-        <v>1.194419718326864</v>
+        <v>1.220385364377447</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05619184753940792</v>
+        <v>0.05515125777015963</v>
       </c>
       <c r="W55">
-        <v>0.2225499623502076</v>
+        <v>0.2227953334177964</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2247673901576317</v>
+        <v>0.2206050310806386</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1799568793614348</v>
+        <v>0.1818568793614348</v>
       </c>
       <c r="C56">
-        <v>-27.77612106757078</v>
+        <v>-30.16747046422464</v>
       </c>
       <c r="D56">
-        <v>45.63987893242921</v>
+        <v>45.00252953577537</v>
       </c>
       <c r="E56">
-        <v>51.416</v>
+        <v>53.17</v>
       </c>
       <c r="F56">
-        <v>94.71599999999999</v>
+        <v>96.47</v>
       </c>
       <c r="G56">
         <v>21.3</v>
@@ -5879,37 +5879,37 @@
         <v>4.927</v>
       </c>
       <c r="M56">
-        <v>22.3340328</v>
+        <v>22.747626</v>
       </c>
       <c r="N56">
-        <v>-17.4070328</v>
+        <v>-17.820626</v>
       </c>
       <c r="O56">
-        <v>-4.3517582</v>
+        <v>-4.4551565</v>
       </c>
       <c r="P56">
-        <v>-13.0552746</v>
+        <v>-13.3654695</v>
       </c>
       <c r="Q56">
-        <v>-12.1822746</v>
+        <v>-12.4924695</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1296682593822276</v>
+        <v>0.1315319984796105</v>
       </c>
       <c r="T56">
-        <v>1.220385364377447</v>
+        <v>1.247505039141391</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05515125777015963</v>
+        <v>0.05414850762888399</v>
       </c>
       <c r="W56">
-        <v>0.2227953334177964</v>
+        <v>0.2230317819011092</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2206050310806386</v>
+        <v>0.2165940305155359</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1818568793614348</v>
+        <v>0.1837568793614348</v>
       </c>
       <c r="C57">
-        <v>-30.16747046422464</v>
+        <v>-32.54126417450388</v>
       </c>
       <c r="D57">
-        <v>45.00252953577537</v>
+        <v>44.38273582549611</v>
       </c>
       <c r="E57">
-        <v>53.17</v>
+        <v>54.92399999999999</v>
       </c>
       <c r="F57">
-        <v>96.47</v>
+        <v>98.22399999999999</v>
       </c>
       <c r="G57">
         <v>21.3</v>
@@ -5961,37 +5961,37 @@
         <v>4.927</v>
       </c>
       <c r="M57">
-        <v>22.747626</v>
+        <v>23.1612192</v>
       </c>
       <c r="N57">
-        <v>-17.820626</v>
+        <v>-18.2342192</v>
       </c>
       <c r="O57">
-        <v>-4.4551565</v>
+        <v>-4.5585548</v>
       </c>
       <c r="P57">
-        <v>-13.3654695</v>
+        <v>-13.6756644</v>
       </c>
       <c r="Q57">
-        <v>-12.4924695</v>
+        <v>-12.8026644</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1315319984796105</v>
+        <v>0.1334804529905107</v>
       </c>
       <c r="T57">
-        <v>1.247505039141391</v>
+        <v>1.275857426394604</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05414850762888399</v>
+        <v>0.05318156999265393</v>
       </c>
       <c r="W57">
-        <v>0.2230317819011092</v>
+        <v>0.2232597857957322</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2165940305155359</v>
+        <v>0.2127262799706157</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1837568793614348</v>
+        <v>0.1856568793614347</v>
       </c>
       <c r="C58">
-        <v>-32.54126417450388</v>
+        <v>-34.89821769708689</v>
       </c>
       <c r="D58">
-        <v>44.38273582549611</v>
+        <v>43.77978230291311</v>
       </c>
       <c r="E58">
-        <v>54.92399999999999</v>
+        <v>56.678</v>
       </c>
       <c r="F58">
-        <v>98.22399999999999</v>
+        <v>99.97799999999999</v>
       </c>
       <c r="G58">
         <v>21.3</v>
@@ -6043,37 +6043,37 @@
         <v>4.927</v>
       </c>
       <c r="M58">
-        <v>23.1612192</v>
+        <v>23.5748124</v>
       </c>
       <c r="N58">
-        <v>-18.2342192</v>
+        <v>-18.6478124</v>
       </c>
       <c r="O58">
-        <v>-4.5585548</v>
+        <v>-4.6619531</v>
       </c>
       <c r="P58">
-        <v>-13.6756644</v>
+        <v>-13.9858593</v>
       </c>
       <c r="Q58">
-        <v>-12.8026644</v>
+        <v>-13.1128593</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1334804529905107</v>
+        <v>0.1355195332926156</v>
       </c>
       <c r="T58">
-        <v>1.275857426394604</v>
+        <v>1.305528529334014</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05318156999265393</v>
+        <v>0.0522485599927828</v>
       </c>
       <c r="W58">
-        <v>0.2232597857957322</v>
+        <v>0.2234797895537018</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2127262799706157</v>
+        <v>0.2089942399711312</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1856568793614347</v>
+        <v>0.1875568793614348</v>
       </c>
       <c r="C59">
-        <v>-34.89821769708689</v>
+        <v>-37.23900817067971</v>
       </c>
       <c r="D59">
-        <v>43.77978230291311</v>
+        <v>43.19299182932029</v>
       </c>
       <c r="E59">
-        <v>56.678</v>
+        <v>58.432</v>
       </c>
       <c r="F59">
-        <v>99.97799999999999</v>
+        <v>101.732</v>
       </c>
       <c r="G59">
         <v>21.3</v>
@@ -6125,37 +6125,37 @@
         <v>4.927</v>
       </c>
       <c r="M59">
-        <v>23.5748124</v>
+        <v>23.9884056</v>
       </c>
       <c r="N59">
-        <v>-18.6478124</v>
+        <v>-19.0614056</v>
       </c>
       <c r="O59">
-        <v>-4.6619531</v>
+        <v>-4.7653514</v>
       </c>
       <c r="P59">
-        <v>-13.9858593</v>
+        <v>-14.2960542</v>
       </c>
       <c r="Q59">
-        <v>-13.1128593</v>
+        <v>-13.4230542</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1355195332926156</v>
+        <v>0.1376557126567255</v>
       </c>
       <c r="T59">
-        <v>1.305528529334014</v>
+        <v>1.336612541937205</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.0522485599927828</v>
+        <v>0.05134772275152793</v>
       </c>
       <c r="W59">
-        <v>0.2234797895537018</v>
+        <v>0.2236922069751897</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2089942399711312</v>
+        <v>0.2053908910061117</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1875568793614348</v>
+        <v>0.1894568793614347</v>
       </c>
       <c r="C60">
-        <v>-37.2390081706797</v>
+        <v>-39.56427691075324</v>
       </c>
       <c r="D60">
-        <v>43.19299182932029</v>
+        <v>42.62172308924674</v>
       </c>
       <c r="E60">
-        <v>58.43199999999999</v>
+        <v>60.18599999999998</v>
       </c>
       <c r="F60">
-        <v>101.732</v>
+        <v>103.486</v>
       </c>
       <c r="G60">
         <v>21.3</v>
@@ -6207,37 +6207,37 @@
         <v>4.927</v>
       </c>
       <c r="M60">
-        <v>23.9884056</v>
+        <v>24.40199879999999</v>
       </c>
       <c r="N60">
-        <v>-19.0614056</v>
+        <v>-19.47499879999999</v>
       </c>
       <c r="O60">
-        <v>-4.765351399999999</v>
+        <v>-4.868749699999999</v>
       </c>
       <c r="P60">
-        <v>-14.2960542</v>
+        <v>-14.6062491</v>
       </c>
       <c r="Q60">
-        <v>-13.4230542</v>
+        <v>-13.7332491</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1376557126567255</v>
+        <v>0.1398960958922554</v>
       </c>
       <c r="T60">
-        <v>1.336612541937204</v>
+        <v>1.369212847838112</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05134772275152794</v>
+        <v>0.05047742236590882</v>
       </c>
       <c r="W60">
-        <v>0.2236922069751897</v>
+        <v>0.2238974238061187</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2053908910061117</v>
+        <v>0.2019096894636353</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1894568793614347</v>
+        <v>0.1913568793614348</v>
       </c>
       <c r="C61">
-        <v>-39.56427691075324</v>
+        <v>-41.87463174760354</v>
       </c>
       <c r="D61">
-        <v>42.62172308924674</v>
+        <v>42.06536825239643</v>
       </c>
       <c r="E61">
-        <v>60.18599999999998</v>
+        <v>61.93999999999998</v>
       </c>
       <c r="F61">
-        <v>103.486</v>
+        <v>105.24</v>
       </c>
       <c r="G61">
         <v>21.3</v>
@@ -6289,37 +6289,37 @@
         <v>4.927</v>
       </c>
       <c r="M61">
-        <v>24.40199879999999</v>
+        <v>24.815592</v>
       </c>
       <c r="N61">
-        <v>-19.47499879999999</v>
+        <v>-19.888592</v>
       </c>
       <c r="O61">
-        <v>-4.868749699999999</v>
+        <v>-4.972147999999999</v>
       </c>
       <c r="P61">
-        <v>-14.6062491</v>
+        <v>-14.916444</v>
       </c>
       <c r="Q61">
-        <v>-13.7332491</v>
+        <v>-14.043444</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1398960958922554</v>
+        <v>0.1422484982895618</v>
       </c>
       <c r="T61">
-        <v>1.369212847838112</v>
+        <v>1.403443169034065</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05047742236590882</v>
+        <v>0.04963613199314367</v>
       </c>
       <c r="W61">
-        <v>0.2238974238061187</v>
+        <v>0.2240958000760167</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2019096894636353</v>
+        <v>0.1985445279725747</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1913568793614348</v>
+        <v>0.1932568793614347</v>
       </c>
       <c r="C62">
-        <v>-41.87463174760354</v>
+        <v>-44.17064918365446</v>
       </c>
       <c r="D62">
-        <v>42.06536825239643</v>
+        <v>41.52335081634553</v>
       </c>
       <c r="E62">
-        <v>61.93999999999998</v>
+        <v>63.69399999999999</v>
       </c>
       <c r="F62">
-        <v>105.24</v>
+        <v>106.994</v>
       </c>
       <c r="G62">
         <v>21.3</v>
@@ -6371,37 +6371,37 @@
         <v>4.927</v>
       </c>
       <c r="M62">
-        <v>24.815592</v>
+        <v>25.2291852</v>
       </c>
       <c r="N62">
-        <v>-19.888592</v>
+        <v>-20.3021852</v>
       </c>
       <c r="O62">
-        <v>-4.972147999999999</v>
+        <v>-5.075546299999999</v>
       </c>
       <c r="P62">
-        <v>-14.916444</v>
+        <v>-15.2266389</v>
       </c>
       <c r="Q62">
-        <v>-14.043444</v>
+        <v>-14.3536389</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1422484982895618</v>
+        <v>0.1447215367072428</v>
       </c>
       <c r="T62">
-        <v>1.403443169034065</v>
+        <v>1.439428891316989</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04963613199314367</v>
+        <v>0.04882242491128885</v>
       </c>
       <c r="W62">
-        <v>0.2240958000760167</v>
+        <v>0.2242876722059181</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1985445279725747</v>
+        <v>0.1952896996451554</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1932568793614347</v>
+        <v>0.1951568793614348</v>
       </c>
       <c r="C63">
-        <v>-44.17064918365446</v>
+        <v>-46.4528763860998</v>
       </c>
       <c r="D63">
-        <v>41.52335081634553</v>
+        <v>40.99512361390018</v>
       </c>
       <c r="E63">
-        <v>63.69399999999999</v>
+        <v>65.44799999999999</v>
       </c>
       <c r="F63">
-        <v>106.994</v>
+        <v>108.748</v>
       </c>
       <c r="G63">
         <v>21.3</v>
@@ -6453,37 +6453,37 @@
         <v>4.927</v>
       </c>
       <c r="M63">
-        <v>25.2291852</v>
+        <v>25.6427784</v>
       </c>
       <c r="N63">
-        <v>-20.3021852</v>
+        <v>-20.7157784</v>
       </c>
       <c r="O63">
-        <v>-5.075546299999999</v>
+        <v>-5.178944599999999</v>
       </c>
       <c r="P63">
-        <v>-15.2266389</v>
+        <v>-15.5368338</v>
       </c>
       <c r="Q63">
-        <v>-14.3536389</v>
+        <v>-14.6638338</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1447215367072428</v>
+        <v>0.147324735041644</v>
       </c>
       <c r="T63">
-        <v>1.439428891316989</v>
+        <v>1.477308598983226</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04882242491128885</v>
+        <v>0.04803496644497774</v>
       </c>
       <c r="W63">
-        <v>0.2242876722059181</v>
+        <v>0.2244733549122743</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1952896996451554</v>
+        <v>0.1921398657799109</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1951568793614348</v>
+        <v>0.1970568793614347</v>
       </c>
       <c r="C64">
-        <v>-46.4528763860998</v>
+        <v>-48.72183302936286</v>
       </c>
       <c r="D64">
-        <v>40.99512361390018</v>
+        <v>40.48016697063712</v>
       </c>
       <c r="E64">
-        <v>65.44799999999999</v>
+        <v>67.20199999999998</v>
       </c>
       <c r="F64">
-        <v>108.748</v>
+        <v>110.502</v>
       </c>
       <c r="G64">
         <v>21.3</v>
@@ -6535,37 +6535,37 @@
         <v>4.927</v>
       </c>
       <c r="M64">
-        <v>25.6427784</v>
+        <v>26.05637159999999</v>
       </c>
       <c r="N64">
-        <v>-20.7157784</v>
+        <v>-21.1293716</v>
       </c>
       <c r="O64">
-        <v>-5.178944599999999</v>
+        <v>-5.282342899999999</v>
       </c>
       <c r="P64">
-        <v>-15.5368338</v>
+        <v>-15.8470287</v>
       </c>
       <c r="Q64">
-        <v>-14.6638338</v>
+        <v>-14.9740287</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.147324735041644</v>
+        <v>0.1500686467995263</v>
       </c>
       <c r="T64">
-        <v>1.477308598983226</v>
+        <v>1.517235858415205</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04803496644497774</v>
+        <v>0.04727250666013683</v>
       </c>
       <c r="W64">
-        <v>0.2244733549122743</v>
+        <v>0.2246531429295398</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1921398657799109</v>
+        <v>0.1890900266405473</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1970568793614347</v>
+        <v>0.1989568793614347</v>
       </c>
       <c r="C65">
-        <v>-48.72183302936286</v>
+        <v>-50.97801300041533</v>
       </c>
       <c r="D65">
-        <v>40.48016697063712</v>
+        <v>39.97798699958466</v>
       </c>
       <c r="E65">
-        <v>67.20199999999998</v>
+        <v>68.95599999999999</v>
       </c>
       <c r="F65">
-        <v>110.502</v>
+        <v>112.256</v>
       </c>
       <c r="G65">
         <v>21.3</v>
@@ -6617,37 +6617,37 @@
         <v>4.927</v>
       </c>
       <c r="M65">
-        <v>26.05637159999999</v>
+        <v>26.4699648</v>
       </c>
       <c r="N65">
-        <v>-21.1293716</v>
+        <v>-21.5429648</v>
       </c>
       <c r="O65">
-        <v>-5.282342899999999</v>
+        <v>-5.385741199999999</v>
       </c>
       <c r="P65">
-        <v>-15.8470287</v>
+        <v>-16.1572236</v>
       </c>
       <c r="Q65">
-        <v>-14.9740287</v>
+        <v>-15.2842236</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1500686467995263</v>
+        <v>0.1529649980995131</v>
       </c>
       <c r="T65">
-        <v>1.517235858415205</v>
+        <v>1.559381298926738</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04727250666013683</v>
+        <v>0.04653387374357219</v>
       </c>
       <c r="W65">
-        <v>0.2246531429295398</v>
+        <v>0.2248273125712657</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1890900266405473</v>
+        <v>0.1861354949742887</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1989568793614347</v>
+        <v>0.2008568793614347</v>
       </c>
       <c r="C66">
-        <v>-50.97801300041533</v>
+        <v>-53.22188597871867</v>
       </c>
       <c r="D66">
-        <v>39.97798699958466</v>
+        <v>39.48811402128131</v>
       </c>
       <c r="E66">
-        <v>68.95599999999999</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="F66">
-        <v>112.256</v>
+        <v>114.01</v>
       </c>
       <c r="G66">
         <v>21.3</v>
@@ -6699,37 +6699,37 @@
         <v>4.927</v>
       </c>
       <c r="M66">
-        <v>26.4699648</v>
+        <v>26.883558</v>
       </c>
       <c r="N66">
-        <v>-21.5429648</v>
+        <v>-21.956558</v>
       </c>
       <c r="O66">
-        <v>-5.385741199999999</v>
+        <v>-5.489139499999999</v>
       </c>
       <c r="P66">
-        <v>-16.1572236</v>
+        <v>-16.4674185</v>
       </c>
       <c r="Q66">
-        <v>-15.2842236</v>
+        <v>-15.5944185</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1529649980995131</v>
+        <v>0.1560268551880706</v>
       </c>
       <c r="T66">
-        <v>1.559381298926738</v>
+        <v>1.603935050324645</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04653387374357219</v>
+        <v>0.04581796799367108</v>
       </c>
       <c r="W66">
-        <v>0.2248273125712657</v>
+        <v>0.2249961231470924</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1861354949742887</v>
+        <v>0.1832718719746843</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2008568793614347</v>
+        <v>0.2027568793614348</v>
       </c>
       <c r="C67">
-        <v>-53.22188597871867</v>
+        <v>-55.45389890141236</v>
       </c>
       <c r="D67">
-        <v>39.48811402128131</v>
+        <v>39.01010109858763</v>
       </c>
       <c r="E67">
-        <v>70.70999999999999</v>
+        <v>72.464</v>
       </c>
       <c r="F67">
-        <v>114.01</v>
+        <v>115.764</v>
       </c>
       <c r="G67">
         <v>21.3</v>
@@ -6781,37 +6781,37 @@
         <v>4.927</v>
       </c>
       <c r="M67">
-        <v>26.883558</v>
+        <v>27.2971512</v>
       </c>
       <c r="N67">
-        <v>-21.956558</v>
+        <v>-22.3701512</v>
       </c>
       <c r="O67">
-        <v>-5.489139499999999</v>
+        <v>-5.592537800000001</v>
       </c>
       <c r="P67">
-        <v>-16.4674185</v>
+        <v>-16.7776134</v>
       </c>
       <c r="Q67">
-        <v>-15.5944185</v>
+        <v>-15.9046134</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1560268551880706</v>
+        <v>0.1592688215171315</v>
       </c>
       <c r="T67">
-        <v>1.603935050324645</v>
+        <v>1.651109610628311</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04581796799367108</v>
+        <v>0.04512375635740332</v>
       </c>
       <c r="W67">
-        <v>0.2249961231470924</v>
+        <v>0.2251598182509243</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1832718719746843</v>
+        <v>0.1804950254296133</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2027568793614348</v>
+        <v>0.2046568793614348</v>
       </c>
       <c r="C68">
-        <v>-55.45389890141236</v>
+        <v>-57.67447732335577</v>
       </c>
       <c r="D68">
-        <v>39.01010109858763</v>
+        <v>38.54352267664421</v>
       </c>
       <c r="E68">
-        <v>72.464</v>
+        <v>74.21799999999999</v>
       </c>
       <c r="F68">
-        <v>115.764</v>
+        <v>117.518</v>
       </c>
       <c r="G68">
         <v>21.3</v>
@@ -6863,37 +6863,37 @@
         <v>4.927</v>
       </c>
       <c r="M68">
-        <v>27.2971512</v>
+        <v>27.7107444</v>
       </c>
       <c r="N68">
-        <v>-22.3701512</v>
+        <v>-22.7837444</v>
       </c>
       <c r="O68">
-        <v>-5.592537800000001</v>
+        <v>-5.6959361</v>
       </c>
       <c r="P68">
-        <v>-16.7776134</v>
+        <v>-17.0878083</v>
       </c>
       <c r="Q68">
-        <v>-15.9046134</v>
+        <v>-16.2148083</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1592688215171315</v>
+        <v>0.1627072706540143</v>
       </c>
       <c r="T68">
-        <v>1.651109610628311</v>
+        <v>1.701143235192806</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04512375635740332</v>
+        <v>0.04445026745654657</v>
       </c>
       <c r="W68">
-        <v>0.2251598182509243</v>
+        <v>0.2253186269337463</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1804950254296133</v>
+        <v>0.1778010698261863</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2046568793614348</v>
+        <v>0.2065568793614348</v>
       </c>
       <c r="C69">
-        <v>-57.67447732335577</v>
+        <v>-59.88402668072401</v>
       </c>
       <c r="D69">
-        <v>38.54352267664421</v>
+        <v>38.08797331927598</v>
       </c>
       <c r="E69">
-        <v>74.21799999999999</v>
+        <v>75.97199999999999</v>
       </c>
       <c r="F69">
-        <v>117.518</v>
+        <v>119.272</v>
       </c>
       <c r="G69">
         <v>21.3</v>
@@ -6945,37 +6945,37 @@
         <v>4.927</v>
       </c>
       <c r="M69">
-        <v>27.7107444</v>
+        <v>28.1243376</v>
       </c>
       <c r="N69">
-        <v>-22.7837444</v>
+        <v>-23.1973376</v>
       </c>
       <c r="O69">
-        <v>-5.6959361</v>
+        <v>-5.7993344</v>
       </c>
       <c r="P69">
-        <v>-17.0878083</v>
+        <v>-17.3980032</v>
       </c>
       <c r="Q69">
-        <v>-16.2148083</v>
+        <v>-16.5250032</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1627072706540143</v>
+        <v>0.1663606228619522</v>
       </c>
       <c r="T69">
-        <v>1.701143235192806</v>
+        <v>1.754303961292581</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04445026745654657</v>
+        <v>0.04379658705277382</v>
       </c>
       <c r="W69">
-        <v>0.2253186269337463</v>
+        <v>0.2254727647729559</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1778010698261863</v>
+        <v>0.1751863482110952</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2065568793614348</v>
+        <v>0.2084568793614348</v>
       </c>
       <c r="C70">
-        <v>-59.88402668072401</v>
+        <v>-62.08293346604246</v>
       </c>
       <c r="D70">
-        <v>38.08797331927598</v>
+        <v>37.64306653395754</v>
       </c>
       <c r="E70">
-        <v>75.97199999999999</v>
+        <v>77.726</v>
       </c>
       <c r="F70">
-        <v>119.272</v>
+        <v>121.026</v>
       </c>
       <c r="G70">
         <v>21.3</v>
@@ -7027,37 +7027,37 @@
         <v>4.927</v>
       </c>
       <c r="M70">
-        <v>28.1243376</v>
+        <v>28.5379308</v>
       </c>
       <c r="N70">
-        <v>-23.1973376</v>
+        <v>-23.6109308</v>
       </c>
       <c r="O70">
-        <v>-5.7993344</v>
+        <v>-5.9027327</v>
       </c>
       <c r="P70">
-        <v>-17.3980032</v>
+        <v>-17.7081981</v>
       </c>
       <c r="Q70">
-        <v>-16.5250032</v>
+        <v>-16.8351981</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1663606228619522</v>
+        <v>0.1702496752123378</v>
       </c>
       <c r="T70">
-        <v>1.754303961292581</v>
+        <v>1.810894411656858</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04379658705277382</v>
+        <v>0.04316185390708144</v>
       </c>
       <c r="W70">
-        <v>0.2254727647729559</v>
+        <v>0.2256224348487102</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1751863482110952</v>
+        <v>0.1726474156283258</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2084568793614348</v>
+        <v>0.2103568793614348</v>
       </c>
       <c r="C71">
-        <v>-62.08293346604246</v>
+        <v>-64.2715663218189</v>
       </c>
       <c r="D71">
-        <v>37.64306653395754</v>
+        <v>37.2084336781811</v>
       </c>
       <c r="E71">
-        <v>77.726</v>
+        <v>79.48</v>
       </c>
       <c r="F71">
-        <v>121.026</v>
+        <v>122.78</v>
       </c>
       <c r="G71">
         <v>21.3</v>
@@ -7109,37 +7109,37 @@
         <v>4.927</v>
       </c>
       <c r="M71">
-        <v>28.5379308</v>
+        <v>28.951524</v>
       </c>
       <c r="N71">
-        <v>-23.6109308</v>
+        <v>-24.024524</v>
       </c>
       <c r="O71">
-        <v>-5.9027327</v>
+        <v>-6.006131000000001</v>
       </c>
       <c r="P71">
-        <v>-17.7081981</v>
+        <v>-18.018393</v>
       </c>
       <c r="Q71">
-        <v>-16.8351981</v>
+        <v>-17.145393</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1702496752123378</v>
+        <v>0.1743979977194157</v>
       </c>
       <c r="T71">
-        <v>1.810894411656858</v>
+        <v>1.871257558712086</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04316185390708144</v>
+        <v>0.04254525599412314</v>
       </c>
       <c r="W71">
-        <v>0.2256224348487102</v>
+        <v>0.2257678286365858</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1726474156283258</v>
+        <v>0.1701810239764925</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2103568793614348</v>
+        <v>0.2122568793614348</v>
       </c>
       <c r="C72">
-        <v>-64.2715663218189</v>
+        <v>-66.45027705927683</v>
       </c>
       <c r="D72">
-        <v>37.2084336781811</v>
+        <v>36.78372294072316</v>
       </c>
       <c r="E72">
-        <v>79.48</v>
+        <v>81.23399999999999</v>
       </c>
       <c r="F72">
-        <v>122.78</v>
+        <v>124.534</v>
       </c>
       <c r="G72">
         <v>21.3</v>
@@ -7191,37 +7191,37 @@
         <v>4.927</v>
       </c>
       <c r="M72">
-        <v>28.951524</v>
+        <v>29.3651172</v>
       </c>
       <c r="N72">
-        <v>-24.024524</v>
+        <v>-24.4381172</v>
       </c>
       <c r="O72">
-        <v>-6.006131000000001</v>
+        <v>-6.1095293</v>
       </c>
       <c r="P72">
-        <v>-18.018393</v>
+        <v>-18.3285879</v>
       </c>
       <c r="Q72">
-        <v>-17.145393</v>
+        <v>-17.4555879</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1743979977194157</v>
+        <v>0.1788324114338784</v>
       </c>
       <c r="T72">
-        <v>1.871257558712086</v>
+        <v>1.935783681426297</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04254525599412314</v>
+        <v>0.04194602703645943</v>
       </c>
       <c r="W72">
-        <v>0.2257678286365858</v>
+        <v>0.2259091268248029</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1701810239764925</v>
+        <v>0.1677841081458378</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2122568793614348</v>
+        <v>0.2141568793614347</v>
       </c>
       <c r="C73">
-        <v>-66.45027705927681</v>
+        <v>-68.619401608107</v>
       </c>
       <c r="D73">
-        <v>36.78372294072316</v>
+        <v>36.36859839189298</v>
       </c>
       <c r="E73">
-        <v>81.23399999999998</v>
+        <v>82.98799999999999</v>
       </c>
       <c r="F73">
-        <v>124.534</v>
+        <v>126.288</v>
       </c>
       <c r="G73">
         <v>21.3</v>
@@ -7273,37 +7273,37 @@
         <v>4.927</v>
       </c>
       <c r="M73">
-        <v>29.3651172</v>
+        <v>29.7787104</v>
       </c>
       <c r="N73">
-        <v>-24.4381172</v>
+        <v>-24.8517104</v>
       </c>
       <c r="O73">
-        <v>-6.109529299999999</v>
+        <v>-6.2129276</v>
       </c>
       <c r="P73">
-        <v>-18.3285879</v>
+        <v>-18.6387828</v>
       </c>
       <c r="Q73">
-        <v>-17.4555879</v>
+        <v>-17.7657828</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1788324114338783</v>
+        <v>0.1835835689850883</v>
       </c>
       <c r="T73">
-        <v>1.935783681426296</v>
+        <v>2.004918812905806</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04194602703645944</v>
+        <v>0.04136344332761972</v>
       </c>
       <c r="W73">
-        <v>0.2259091268248029</v>
+        <v>0.2260465000633473</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1677841081458378</v>
+        <v>0.1654537733104788</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2141568793614347</v>
+        <v>0.2160568793614348</v>
       </c>
       <c r="C74">
-        <v>-68.619401608107</v>
+        <v>-70.77926090262577</v>
       </c>
       <c r="D74">
-        <v>36.36859839189298</v>
+        <v>35.9627390973742</v>
       </c>
       <c r="E74">
-        <v>82.98799999999999</v>
+        <v>84.74199999999998</v>
       </c>
       <c r="F74">
-        <v>126.288</v>
+        <v>128.042</v>
       </c>
       <c r="G74">
         <v>21.3</v>
@@ -7355,37 +7355,37 @@
         <v>4.927</v>
       </c>
       <c r="M74">
-        <v>29.7787104</v>
+        <v>30.1923036</v>
       </c>
       <c r="N74">
-        <v>-24.8517104</v>
+        <v>-25.2653036</v>
       </c>
       <c r="O74">
-        <v>-6.2129276</v>
+        <v>-6.316325899999999</v>
       </c>
       <c r="P74">
-        <v>-18.6387828</v>
+        <v>-18.9489777</v>
       </c>
       <c r="Q74">
-        <v>-17.7657828</v>
+        <v>-18.0759777</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1835835689850883</v>
+        <v>0.1886866641326841</v>
       </c>
       <c r="T74">
-        <v>2.004918812905806</v>
+        <v>2.079175065235651</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04136344332761972</v>
+        <v>0.04079682081628247</v>
       </c>
       <c r="W74">
-        <v>0.2260465000633473</v>
+        <v>0.2261801096515206</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1654537733104788</v>
+        <v>0.1631872832651299</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2160568793614348</v>
+        <v>0.2179568793614347</v>
       </c>
       <c r="C75">
-        <v>-70.77926090262577</v>
+        <v>-72.93016170925317</v>
       </c>
       <c r="D75">
-        <v>35.9627390973742</v>
+        <v>35.56583829074682</v>
       </c>
       <c r="E75">
-        <v>84.74199999999998</v>
+        <v>86.496</v>
       </c>
       <c r="F75">
-        <v>128.042</v>
+        <v>129.796</v>
       </c>
       <c r="G75">
         <v>21.3</v>
@@ -7437,37 +7437,37 @@
         <v>4.927</v>
       </c>
       <c r="M75">
-        <v>30.1923036</v>
+        <v>30.6058968</v>
       </c>
       <c r="N75">
-        <v>-25.2653036</v>
+        <v>-25.6788968</v>
       </c>
       <c r="O75">
-        <v>-6.316325899999999</v>
+        <v>-6.4197242</v>
       </c>
       <c r="P75">
-        <v>-18.9489777</v>
+        <v>-19.2591726</v>
       </c>
       <c r="Q75">
-        <v>-18.0759777</v>
+        <v>-18.3861726</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1886866641326841</v>
+        <v>0.1941823050608643</v>
       </c>
       <c r="T75">
-        <v>2.079175065235651</v>
+        <v>2.159143336975484</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04079682081628247</v>
+        <v>0.04024551242687324</v>
       </c>
       <c r="W75">
-        <v>0.2261801096515206</v>
+        <v>0.2263101081697433</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1631872832651299</v>
+        <v>0.160982049707493</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2179568793614347</v>
+        <v>0.2198568793614348</v>
       </c>
       <c r="C76">
-        <v>-72.93016170925317</v>
+        <v>-75.07239739979488</v>
       </c>
       <c r="D76">
-        <v>35.56583829074682</v>
+        <v>35.17760260020511</v>
       </c>
       <c r="E76">
-        <v>86.496</v>
+        <v>88.24999999999999</v>
       </c>
       <c r="F76">
-        <v>129.796</v>
+        <v>131.55</v>
       </c>
       <c r="G76">
         <v>21.3</v>
@@ -7519,37 +7519,37 @@
         <v>4.927</v>
       </c>
       <c r="M76">
-        <v>30.6058968</v>
+        <v>31.01949</v>
       </c>
       <c r="N76">
-        <v>-25.6788968</v>
+        <v>-26.09249</v>
       </c>
       <c r="O76">
-        <v>-6.4197242</v>
+        <v>-6.523122499999999</v>
       </c>
       <c r="P76">
-        <v>-19.2591726</v>
+        <v>-19.5693675</v>
       </c>
       <c r="Q76">
-        <v>-18.3861726</v>
+        <v>-18.6963675</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1941823050608643</v>
+        <v>0.2001175972632989</v>
       </c>
       <c r="T76">
-        <v>2.159143336975484</v>
+        <v>2.245509070454503</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04024551242687324</v>
+        <v>0.03970890559451493</v>
       </c>
       <c r="W76">
-        <v>0.2263101081697433</v>
+        <v>0.2264366400608134</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.160982049707493</v>
+        <v>0.1588356223780597</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2198568793614348</v>
+        <v>0.2217568793614348</v>
       </c>
       <c r="C77">
-        <v>-75.07239739979488</v>
+        <v>-77.20624867462395</v>
       </c>
       <c r="D77">
-        <v>35.17760260020511</v>
+        <v>34.79775132537602</v>
       </c>
       <c r="E77">
-        <v>88.24999999999999</v>
+        <v>90.00399999999998</v>
       </c>
       <c r="F77">
-        <v>131.55</v>
+        <v>133.304</v>
       </c>
       <c r="G77">
         <v>21.3</v>
@@ -7601,37 +7601,37 @@
         <v>4.927</v>
       </c>
       <c r="M77">
-        <v>31.01949</v>
+        <v>31.4330832</v>
       </c>
       <c r="N77">
-        <v>-26.09249</v>
+        <v>-26.5060832</v>
       </c>
       <c r="O77">
-        <v>-6.523122499999999</v>
+        <v>-6.626520799999999</v>
       </c>
       <c r="P77">
-        <v>-19.5693675</v>
+        <v>-19.8795624</v>
       </c>
       <c r="Q77">
-        <v>-18.6963675</v>
+        <v>-19.0065624</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2001175972632989</v>
+        <v>0.2065474971492697</v>
       </c>
       <c r="T77">
-        <v>2.245509070454503</v>
+        <v>2.339071948390108</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03970890559451493</v>
+        <v>0.03918641999458711</v>
       </c>
       <c r="W77">
-        <v>0.2264366400608134</v>
+        <v>0.2265598421652764</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1588356223780597</v>
+        <v>0.1567456799783484</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2217568793614348</v>
+        <v>0.2236568793614347</v>
       </c>
       <c r="C78">
-        <v>-77.20624867462395</v>
+        <v>-79.33198423950958</v>
       </c>
       <c r="D78">
-        <v>34.79775132537602</v>
+        <v>34.42601576049042</v>
       </c>
       <c r="E78">
-        <v>90.00399999999998</v>
+        <v>91.758</v>
       </c>
       <c r="F78">
-        <v>133.304</v>
+        <v>135.058</v>
       </c>
       <c r="G78">
         <v>21.3</v>
@@ -7683,37 +7683,37 @@
         <v>4.927</v>
       </c>
       <c r="M78">
-        <v>31.4330832</v>
+        <v>31.8466764</v>
       </c>
       <c r="N78">
-        <v>-26.5060832</v>
+        <v>-26.9196764</v>
       </c>
       <c r="O78">
-        <v>-6.626520799999999</v>
+        <v>-6.7299191</v>
       </c>
       <c r="P78">
-        <v>-19.8795624</v>
+        <v>-20.1897573</v>
       </c>
       <c r="Q78">
-        <v>-19.0065624</v>
+        <v>-19.3167573</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2065474971492697</v>
+        <v>0.2135365187644553</v>
       </c>
       <c r="T78">
-        <v>2.339071948390108</v>
+        <v>2.440770728754895</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03918641999458711</v>
+        <v>0.03867750544920286</v>
       </c>
       <c r="W78">
-        <v>0.2265598421652764</v>
+        <v>0.226679844215078</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1567456799783484</v>
+        <v>0.1547100217968114</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2236568793614347</v>
+        <v>0.2255568793614348</v>
       </c>
       <c r="C79">
-        <v>-79.33198423950958</v>
+        <v>-81.44986143952156</v>
       </c>
       <c r="D79">
-        <v>34.42601576049042</v>
+        <v>34.06213856047842</v>
       </c>
       <c r="E79">
-        <v>91.758</v>
+        <v>93.51199999999999</v>
       </c>
       <c r="F79">
-        <v>135.058</v>
+        <v>136.812</v>
       </c>
       <c r="G79">
         <v>21.3</v>
@@ -7765,37 +7765,37 @@
         <v>4.927</v>
       </c>
       <c r="M79">
-        <v>31.8466764</v>
+        <v>32.2602696</v>
       </c>
       <c r="N79">
-        <v>-26.9196764</v>
+        <v>-27.3332696</v>
       </c>
       <c r="O79">
-        <v>-6.7299191</v>
+        <v>-6.8333174</v>
       </c>
       <c r="P79">
-        <v>-20.1897573</v>
+        <v>-20.4999522</v>
       </c>
       <c r="Q79">
-        <v>-19.3167573</v>
+        <v>-19.6269522</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2135365187644553</v>
+        <v>0.2211609059810214</v>
       </c>
       <c r="T79">
-        <v>2.440770728754895</v>
+        <v>2.551714852789209</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03867750544920286</v>
+        <v>0.0381816399947259</v>
       </c>
       <c r="W79">
-        <v>0.226679844215078</v>
+        <v>0.2267967692892436</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1547100217968114</v>
+        <v>0.1527265599789036</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2255568793614348</v>
+        <v>0.2274568793614348</v>
       </c>
       <c r="C80">
-        <v>-81.44986143952156</v>
+        <v>-83.56012685315416</v>
       </c>
       <c r="D80">
-        <v>34.06213856047842</v>
+        <v>33.70587314684582</v>
       </c>
       <c r="E80">
-        <v>93.51199999999999</v>
+        <v>95.26599999999998</v>
       </c>
       <c r="F80">
-        <v>136.812</v>
+        <v>138.566</v>
       </c>
       <c r="G80">
         <v>21.3</v>
@@ -7847,37 +7847,37 @@
         <v>4.927</v>
       </c>
       <c r="M80">
-        <v>32.2602696</v>
+        <v>32.67386279999999</v>
       </c>
       <c r="N80">
-        <v>-27.3332696</v>
+        <v>-27.7468628</v>
       </c>
       <c r="O80">
-        <v>-6.8333174</v>
+        <v>-6.936715699999999</v>
       </c>
       <c r="P80">
-        <v>-20.4999522</v>
+        <v>-20.81014709999999</v>
       </c>
       <c r="Q80">
-        <v>-19.6269522</v>
+        <v>-19.93714709999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2211609059810214</v>
+        <v>0.2295114253134511</v>
       </c>
       <c r="T80">
-        <v>2.551714852789209</v>
+        <v>2.673225083874409</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0381816399947259</v>
+        <v>0.03769832809605848</v>
       </c>
       <c r="W80">
-        <v>0.2267967692892436</v>
+        <v>0.2269107342349494</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1527265599789036</v>
+        <v>0.1507933123842339</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2274568793614348</v>
+        <v>0.2293568793614348</v>
       </c>
       <c r="C81">
-        <v>-83.56012685315416</v>
+        <v>-85.66301684955091</v>
       </c>
       <c r="D81">
-        <v>33.70587314684582</v>
+        <v>33.35698315044908</v>
       </c>
       <c r="E81">
-        <v>95.26599999999998</v>
+        <v>97.02</v>
       </c>
       <c r="F81">
-        <v>138.566</v>
+        <v>140.32</v>
       </c>
       <c r="G81">
         <v>21.3</v>
@@ -7929,37 +7929,37 @@
         <v>4.927</v>
       </c>
       <c r="M81">
-        <v>32.67386279999999</v>
+        <v>33.087456</v>
       </c>
       <c r="N81">
-        <v>-27.7468628</v>
+        <v>-28.160456</v>
       </c>
       <c r="O81">
-        <v>-6.936715699999999</v>
+        <v>-7.040114000000001</v>
       </c>
       <c r="P81">
-        <v>-20.81014709999999</v>
+        <v>-21.120342</v>
       </c>
       <c r="Q81">
-        <v>-19.93714709999999</v>
+        <v>-20.247342</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2295114253134511</v>
+        <v>0.2386969965791236</v>
       </c>
       <c r="T81">
-        <v>2.673225083874409</v>
+        <v>2.806886338068129</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03769832809605848</v>
+        <v>0.03722709899485774</v>
       </c>
       <c r="W81">
-        <v>0.2269107342349494</v>
+        <v>0.2270218500570126</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1507933123842339</v>
+        <v>0.148908395979431</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2293568793614348</v>
+        <v>0.2312568793614347</v>
       </c>
       <c r="C82">
-        <v>-85.66301684955091</v>
+        <v>-87.75875811147699</v>
       </c>
       <c r="D82">
-        <v>33.35698315044908</v>
+        <v>33.01524188852299</v>
       </c>
       <c r="E82">
-        <v>97.02</v>
+        <v>98.77399999999999</v>
       </c>
       <c r="F82">
-        <v>140.32</v>
+        <v>142.074</v>
       </c>
       <c r="G82">
         <v>21.3</v>
@@ -8011,37 +8011,37 @@
         <v>4.927</v>
       </c>
       <c r="M82">
-        <v>33.087456</v>
+        <v>33.5010492</v>
       </c>
       <c r="N82">
-        <v>-28.160456</v>
+        <v>-28.5740492</v>
       </c>
       <c r="O82">
-        <v>-7.040114000000001</v>
+        <v>-7.143512299999999</v>
       </c>
       <c r="P82">
-        <v>-21.120342</v>
+        <v>-21.4305369</v>
       </c>
       <c r="Q82">
-        <v>-20.247342</v>
+        <v>-20.5575369</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2386969965791236</v>
+        <v>0.248849470083288</v>
       </c>
       <c r="T82">
-        <v>2.806886338068129</v>
+        <v>2.954617197966452</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03722709899485774</v>
+        <v>0.03676750518010642</v>
       </c>
       <c r="W82">
-        <v>0.2270218500570126</v>
+        <v>0.2271302222785309</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.148908395979431</v>
+        <v>0.1470700207204256</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2312568793614347</v>
+        <v>0.2331568793614348</v>
       </c>
       <c r="C83">
-        <v>-87.75875811147699</v>
+        <v>-89.84756812647082</v>
       </c>
       <c r="D83">
-        <v>33.01524188852299</v>
+        <v>32.68043187352918</v>
       </c>
       <c r="E83">
-        <v>98.77399999999999</v>
+        <v>100.528</v>
       </c>
       <c r="F83">
-        <v>142.074</v>
+        <v>143.828</v>
       </c>
       <c r="G83">
         <v>21.3</v>
@@ -8093,37 +8093,37 @@
         <v>4.927</v>
       </c>
       <c r="M83">
-        <v>33.5010492</v>
+        <v>33.91464240000001</v>
       </c>
       <c r="N83">
-        <v>-28.5740492</v>
+        <v>-28.98764240000001</v>
       </c>
       <c r="O83">
-        <v>-7.143512299999999</v>
+        <v>-7.246910600000001</v>
       </c>
       <c r="P83">
-        <v>-21.4305369</v>
+        <v>-21.74073180000001</v>
       </c>
       <c r="Q83">
-        <v>-20.5575369</v>
+        <v>-20.8677318</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.248849470083288</v>
+        <v>0.2601299961990263</v>
       </c>
       <c r="T83">
-        <v>2.954617197966452</v>
+        <v>3.118762597853478</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03676750518010642</v>
+        <v>0.03631912097059291</v>
       </c>
       <c r="W83">
-        <v>0.2271302222785309</v>
+        <v>0.2272359512751342</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1470700207204256</v>
+        <v>0.1452764838823717</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2331568793614348</v>
+        <v>0.2350568793614348</v>
       </c>
       <c r="C84">
-        <v>-89.84756812647082</v>
+        <v>-91.92965564841036</v>
       </c>
       <c r="D84">
-        <v>32.68043187352918</v>
+        <v>32.35234435158963</v>
       </c>
       <c r="E84">
-        <v>100.528</v>
+        <v>102.282</v>
       </c>
       <c r="F84">
-        <v>143.828</v>
+        <v>145.582</v>
       </c>
       <c r="G84">
         <v>21.3</v>
@@ -8175,37 +8175,37 @@
         <v>4.927</v>
       </c>
       <c r="M84">
-        <v>33.91464240000001</v>
+        <v>34.3282356</v>
       </c>
       <c r="N84">
-        <v>-28.98764240000001</v>
+        <v>-29.4012356</v>
       </c>
       <c r="O84">
-        <v>-7.246910600000001</v>
+        <v>-7.3503089</v>
       </c>
       <c r="P84">
-        <v>-21.74073180000001</v>
+        <v>-22.0509267</v>
       </c>
       <c r="Q84">
-        <v>-20.8677318</v>
+        <v>-21.1779267</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2601299961990263</v>
+        <v>0.2727376430342631</v>
       </c>
       <c r="T84">
-        <v>3.118762597853478</v>
+        <v>3.302219221256623</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03631912097059291</v>
+        <v>0.03588154119986289</v>
       </c>
       <c r="W84">
-        <v>0.2272359512751342</v>
+        <v>0.2273391325850724</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1452764838823717</v>
+        <v>0.1435261647994516</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2350568793614348</v>
+        <v>0.2369568793614348</v>
       </c>
       <c r="C85">
-        <v>-91.92965564841036</v>
+        <v>-94.00522113155363</v>
       </c>
       <c r="D85">
-        <v>32.35234435158963</v>
+        <v>32.03077886844636</v>
       </c>
       <c r="E85">
-        <v>102.282</v>
+        <v>104.036</v>
       </c>
       <c r="F85">
-        <v>145.582</v>
+        <v>147.336</v>
       </c>
       <c r="G85">
         <v>21.3</v>
@@ -8257,37 +8257,37 @@
         <v>4.927</v>
       </c>
       <c r="M85">
-        <v>34.3282356</v>
+        <v>34.7418288</v>
       </c>
       <c r="N85">
-        <v>-29.4012356</v>
+        <v>-29.8148288</v>
       </c>
       <c r="O85">
-        <v>-7.3503089</v>
+        <v>-7.4537072</v>
       </c>
       <c r="P85">
-        <v>-22.0509267</v>
+        <v>-22.3611216</v>
       </c>
       <c r="Q85">
-        <v>-21.1779267</v>
+        <v>-21.4881216</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2727376430342631</v>
+        <v>0.2869212457239046</v>
       </c>
       <c r="T85">
-        <v>3.302219221256623</v>
+        <v>3.508607922585163</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03588154119986289</v>
+        <v>0.03545437999510261</v>
       </c>
       <c r="W85">
-        <v>0.2273391325850724</v>
+        <v>0.2274398571971548</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1435261647994516</v>
+        <v>0.1418175199804105</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2369568793614348</v>
+        <v>0.2388568793614347</v>
       </c>
       <c r="C86">
-        <v>-94.00522113155363</v>
+        <v>-96.07445713894867</v>
       </c>
       <c r="D86">
-        <v>32.03077886844636</v>
+        <v>31.7155428610513</v>
       </c>
       <c r="E86">
-        <v>104.036</v>
+        <v>105.79</v>
       </c>
       <c r="F86">
-        <v>147.336</v>
+        <v>149.09</v>
       </c>
       <c r="G86">
         <v>21.3</v>
@@ -8339,37 +8339,37 @@
         <v>4.927</v>
       </c>
       <c r="M86">
-        <v>34.7418288</v>
+        <v>35.15542199999999</v>
       </c>
       <c r="N86">
-        <v>-29.8148288</v>
+        <v>-30.22842199999999</v>
       </c>
       <c r="O86">
-        <v>-7.4537072</v>
+        <v>-7.557105499999999</v>
       </c>
       <c r="P86">
-        <v>-22.3611216</v>
+        <v>-22.6713165</v>
       </c>
       <c r="Q86">
-        <v>-21.4881216</v>
+        <v>-21.79831649999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2869212457239044</v>
+        <v>0.3029959954388314</v>
       </c>
       <c r="T86">
-        <v>3.508607922585161</v>
+        <v>3.742515117424171</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03545437999510261</v>
+        <v>0.03503726964221906</v>
       </c>
       <c r="W86">
-        <v>0.2274398571971548</v>
+        <v>0.2275382118183648</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1418175199804105</v>
+        <v>0.1401490785688763</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2388568793614347</v>
+        <v>0.2407568793614348</v>
       </c>
       <c r="C87">
-        <v>-96.07445713894867</v>
+        <v>-98.13754872696224</v>
       </c>
       <c r="D87">
-        <v>31.7155428610513</v>
+        <v>31.40645127303772</v>
       </c>
       <c r="E87">
-        <v>105.79</v>
+        <v>107.544</v>
       </c>
       <c r="F87">
-        <v>149.09</v>
+        <v>150.844</v>
       </c>
       <c r="G87">
         <v>21.3</v>
@@ -8421,37 +8421,37 @@
         <v>4.927</v>
       </c>
       <c r="M87">
-        <v>35.15542199999999</v>
+        <v>35.5690152</v>
       </c>
       <c r="N87">
-        <v>-30.22842199999999</v>
+        <v>-30.6420152</v>
       </c>
       <c r="O87">
-        <v>-7.557105499999999</v>
+        <v>-7.660503799999999</v>
       </c>
       <c r="P87">
-        <v>-22.6713165</v>
+        <v>-22.9815114</v>
       </c>
       <c r="Q87">
-        <v>-21.79831649999999</v>
+        <v>-22.10851139999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3029959954388314</v>
+        <v>0.3213671379701765</v>
       </c>
       <c r="T87">
-        <v>3.742515117424171</v>
+        <v>4.009837625811612</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03503726964221906</v>
+        <v>0.03462985953010023</v>
       </c>
       <c r="W87">
-        <v>0.2275382118183648</v>
+        <v>0.2276342791228024</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1401490785688763</v>
+        <v>0.1385194381204009</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2407568793614348</v>
+        <v>0.2426568793614348</v>
       </c>
       <c r="C88">
-        <v>-98.13754872696224</v>
+        <v>-100.1946738075403</v>
       </c>
       <c r="D88">
-        <v>31.40645127303772</v>
+        <v>31.1033261924597</v>
       </c>
       <c r="E88">
-        <v>107.544</v>
+        <v>109.298</v>
       </c>
       <c r="F88">
-        <v>150.844</v>
+        <v>152.598</v>
       </c>
       <c r="G88">
         <v>21.3</v>
@@ -8503,37 +8503,37 @@
         <v>4.927</v>
       </c>
       <c r="M88">
-        <v>35.5690152</v>
+        <v>35.9826084</v>
       </c>
       <c r="N88">
-        <v>-30.6420152</v>
+        <v>-31.0556084</v>
       </c>
       <c r="O88">
-        <v>-7.660503799999999</v>
+        <v>-7.763902099999999</v>
       </c>
       <c r="P88">
-        <v>-22.9815114</v>
+        <v>-23.2917063</v>
       </c>
       <c r="Q88">
-        <v>-22.10851139999999</v>
+        <v>-22.4187063</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3213671379701765</v>
+        <v>0.3425646101217286</v>
       </c>
       <c r="T88">
-        <v>4.009837625811612</v>
+        <v>4.318286673950968</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03462985953010023</v>
+        <v>0.03423181516768529</v>
       </c>
       <c r="W88">
-        <v>0.2276342791228024</v>
+        <v>0.2277281379834598</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1385194381204009</v>
+        <v>0.1369272606707411</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2426568793614348</v>
+        <v>0.2445568793614348</v>
       </c>
       <c r="C89">
-        <v>-100.1946738075403</v>
+        <v>-102.2460034896903</v>
       </c>
       <c r="D89">
-        <v>31.1033261924597</v>
+        <v>30.80599651030964</v>
       </c>
       <c r="E89">
-        <v>109.298</v>
+        <v>111.052</v>
       </c>
       <c r="F89">
-        <v>152.598</v>
+        <v>154.352</v>
       </c>
       <c r="G89">
         <v>21.3</v>
@@ -8585,37 +8585,37 @@
         <v>4.927</v>
       </c>
       <c r="M89">
-        <v>35.9826084</v>
+        <v>36.3962016</v>
       </c>
       <c r="N89">
-        <v>-31.0556084</v>
+        <v>-31.4692016</v>
       </c>
       <c r="O89">
-        <v>-7.763902099999999</v>
+        <v>-7.8673004</v>
       </c>
       <c r="P89">
-        <v>-23.2917063</v>
+        <v>-23.6019012</v>
       </c>
       <c r="Q89">
-        <v>-22.4187063</v>
+        <v>-22.7289012</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3425646101217286</v>
+        <v>0.3672949942985393</v>
       </c>
       <c r="T89">
-        <v>4.318286673950968</v>
+        <v>4.678143896780216</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03423181516768529</v>
+        <v>0.0338428172680525</v>
       </c>
       <c r="W89">
-        <v>0.2277281379834598</v>
+        <v>0.2278198636881932</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1369272606707411</v>
+        <v>0.13537126907221</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2445568793614348</v>
+        <v>0.2464568793614348</v>
       </c>
       <c r="C90">
-        <v>-102.2460034896903</v>
+        <v>-104.2917024015635</v>
       </c>
       <c r="D90">
-        <v>30.80599651030964</v>
+        <v>30.51429759843652</v>
       </c>
       <c r="E90">
-        <v>111.052</v>
+        <v>112.806</v>
       </c>
       <c r="F90">
-        <v>154.352</v>
+        <v>156.106</v>
       </c>
       <c r="G90">
         <v>21.3</v>
@@ -8667,37 +8667,37 @@
         <v>4.927</v>
       </c>
       <c r="M90">
-        <v>36.3962016</v>
+        <v>36.8097948</v>
       </c>
       <c r="N90">
-        <v>-31.4692016</v>
+        <v>-31.8827948</v>
       </c>
       <c r="O90">
-        <v>-7.8673004</v>
+        <v>-7.9706987</v>
       </c>
       <c r="P90">
-        <v>-23.6019012</v>
+        <v>-23.9120961</v>
       </c>
       <c r="Q90">
-        <v>-22.7289012</v>
+        <v>-23.0390961</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3672949942985393</v>
+        <v>0.3965218119620429</v>
       </c>
       <c r="T90">
-        <v>4.678143896780216</v>
+        <v>5.103429705578417</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0338428172680525</v>
+        <v>0.03346256089425415</v>
       </c>
       <c r="W90">
-        <v>0.2278198636881932</v>
+        <v>0.2279095281411349</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.13537126907221</v>
+        <v>0.1338502435770166</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2464568793614348</v>
+        <v>0.2483568793614348</v>
       </c>
       <c r="C91">
-        <v>-104.2917024015635</v>
+        <v>-106.3319289944089</v>
       </c>
       <c r="D91">
-        <v>30.51429759843652</v>
+        <v>30.22807100559106</v>
       </c>
       <c r="E91">
-        <v>112.806</v>
+        <v>114.56</v>
       </c>
       <c r="F91">
-        <v>156.106</v>
+        <v>157.86</v>
       </c>
       <c r="G91">
         <v>21.3</v>
@@ -8749,37 +8749,37 @@
         <v>4.927</v>
       </c>
       <c r="M91">
-        <v>36.8097948</v>
+        <v>37.223388</v>
       </c>
       <c r="N91">
-        <v>-31.8827948</v>
+        <v>-32.296388</v>
       </c>
       <c r="O91">
-        <v>-7.9706987</v>
+        <v>-8.074097</v>
       </c>
       <c r="P91">
-        <v>-23.9120961</v>
+        <v>-24.222291</v>
       </c>
       <c r="Q91">
-        <v>-23.0390961</v>
+        <v>-23.349291</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3965218119620429</v>
+        <v>0.4315939931582472</v>
       </c>
       <c r="T91">
-        <v>5.103429705578417</v>
+        <v>5.613772676136259</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03346256089425415</v>
+        <v>0.03309075466209577</v>
       </c>
       <c r="W91">
-        <v>0.2279095281411349</v>
+        <v>0.2279972000506778</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1338502435770166</v>
+        <v>0.1323630186483831</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2483568793614348</v>
+        <v>0.2502568793614348</v>
       </c>
       <c r="C92">
-        <v>-106.3319289944089</v>
+        <v>-108.3668358295812</v>
       </c>
       <c r="D92">
-        <v>30.22807100559106</v>
+        <v>29.94716417041878</v>
       </c>
       <c r="E92">
-        <v>114.56</v>
+        <v>116.314</v>
       </c>
       <c r="F92">
-        <v>157.86</v>
+        <v>159.614</v>
       </c>
       <c r="G92">
         <v>21.3</v>
@@ -8831,37 +8831,37 @@
         <v>4.927</v>
       </c>
       <c r="M92">
-        <v>37.223388</v>
+        <v>37.63698119999999</v>
       </c>
       <c r="N92">
-        <v>-32.296388</v>
+        <v>-32.70998119999999</v>
       </c>
       <c r="O92">
-        <v>-8.074097</v>
+        <v>-8.177495299999999</v>
       </c>
       <c r="P92">
-        <v>-24.222291</v>
+        <v>-24.5324859</v>
       </c>
       <c r="Q92">
-        <v>-23.349291</v>
+        <v>-23.6594859</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4315939931582472</v>
+        <v>0.4744599923980525</v>
       </c>
       <c r="T92">
-        <v>5.613772676136259</v>
+        <v>6.237525195706955</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03309075466209577</v>
+        <v>0.03272711999547934</v>
       </c>
       <c r="W92">
-        <v>0.2279972000506778</v>
+        <v>0.228082945105066</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1323630186483831</v>
+        <v>0.1309084799819173</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2502568793614348</v>
+        <v>0.2521568793614347</v>
       </c>
       <c r="C93">
-        <v>-108.3668358295812</v>
+        <v>-110.3965698496917</v>
       </c>
       <c r="D93">
-        <v>29.94716417041878</v>
+        <v>29.67143015030825</v>
       </c>
       <c r="E93">
-        <v>116.314</v>
+        <v>118.068</v>
       </c>
       <c r="F93">
-        <v>159.614</v>
+        <v>161.368</v>
       </c>
       <c r="G93">
         <v>21.3</v>
@@ -8913,37 +8913,37 @@
         <v>4.927</v>
       </c>
       <c r="M93">
-        <v>37.63698119999999</v>
+        <v>38.0505744</v>
       </c>
       <c r="N93">
-        <v>-32.70998119999999</v>
+        <v>-33.1235744</v>
       </c>
       <c r="O93">
-        <v>-8.177495299999999</v>
+        <v>-8.280893600000001</v>
       </c>
       <c r="P93">
-        <v>-24.5324859</v>
+        <v>-24.8426808</v>
       </c>
       <c r="Q93">
-        <v>-23.6594859</v>
+        <v>-23.9696808</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4744599923980525</v>
+        <v>0.5280424914478091</v>
       </c>
       <c r="T93">
-        <v>6.237525195706955</v>
+        <v>7.017215845170326</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03272711999547934</v>
+        <v>0.03237139043031108</v>
       </c>
       <c r="W93">
-        <v>0.228082945105066</v>
+        <v>0.2281668261365326</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1309084799819173</v>
+        <v>0.1294855617212444</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2521568793614347</v>
+        <v>0.2540568793614348</v>
       </c>
       <c r="C94">
-        <v>-110.3965698496917</v>
+        <v>-112.4212726349176</v>
       </c>
       <c r="D94">
-        <v>29.67143015030825</v>
+        <v>29.40072736508238</v>
       </c>
       <c r="E94">
-        <v>118.068</v>
+        <v>119.822</v>
       </c>
       <c r="F94">
-        <v>161.368</v>
+        <v>163.122</v>
       </c>
       <c r="G94">
         <v>21.3</v>
@@ -8995,37 +8995,37 @@
         <v>4.927</v>
       </c>
       <c r="M94">
-        <v>38.0505744</v>
+        <v>38.4641676</v>
       </c>
       <c r="N94">
-        <v>-33.1235744</v>
+        <v>-33.5371676</v>
       </c>
       <c r="O94">
-        <v>-8.280893600000001</v>
+        <v>-8.384291899999999</v>
       </c>
       <c r="P94">
-        <v>-24.8426808</v>
+        <v>-25.1528757</v>
       </c>
       <c r="Q94">
-        <v>-23.9696808</v>
+        <v>-24.27987569999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5280424914478091</v>
+        <v>0.5969342759403534</v>
       </c>
       <c r="T94">
-        <v>7.017215845170326</v>
+        <v>8.019675251623232</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03237139043031108</v>
+        <v>0.03202331096331849</v>
       </c>
       <c r="W94">
-        <v>0.2281668261365326</v>
+        <v>0.2282489032748495</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1294855617212444</v>
+        <v>0.128093243853274</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2540568793614348</v>
+        <v>0.2559568793614347</v>
       </c>
       <c r="C95">
-        <v>-112.4212726349176</v>
+        <v>-114.4410806454067</v>
       </c>
       <c r="D95">
-        <v>29.40072736508238</v>
+        <v>29.13491935459329</v>
       </c>
       <c r="E95">
-        <v>119.822</v>
+        <v>121.576</v>
       </c>
       <c r="F95">
-        <v>163.122</v>
+        <v>164.876</v>
       </c>
       <c r="G95">
         <v>21.3</v>
@@ -9077,37 +9077,37 @@
         <v>4.927</v>
       </c>
       <c r="M95">
-        <v>38.4641676</v>
+        <v>38.8777608</v>
       </c>
       <c r="N95">
-        <v>-33.5371676</v>
+        <v>-33.9507608</v>
       </c>
       <c r="O95">
-        <v>-8.384291899999999</v>
+        <v>-8.487690199999999</v>
       </c>
       <c r="P95">
-        <v>-25.1528757</v>
+        <v>-25.4630706</v>
       </c>
       <c r="Q95">
-        <v>-24.27987569999999</v>
+        <v>-24.5900706</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5969342759403534</v>
+        <v>0.6887899885970791</v>
       </c>
       <c r="T95">
-        <v>8.019675251623232</v>
+        <v>9.356287793560439</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03202331096331849</v>
+        <v>0.03168263744243213</v>
       </c>
       <c r="W95">
-        <v>0.2282489032748495</v>
+        <v>0.2283292340910745</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.128093243853274</v>
+        <v>0.1267305497697285</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2559568793614347</v>
+        <v>0.2578568793614348</v>
       </c>
       <c r="C96">
-        <v>-114.4410806454067</v>
+        <v>-116.4561254506515</v>
       </c>
       <c r="D96">
-        <v>29.13491935459329</v>
+        <v>28.8738745493485</v>
       </c>
       <c r="E96">
-        <v>121.576</v>
+        <v>123.33</v>
       </c>
       <c r="F96">
-        <v>164.876</v>
+        <v>166.63</v>
       </c>
       <c r="G96">
         <v>21.3</v>
@@ -9159,37 +9159,37 @@
         <v>4.927</v>
       </c>
       <c r="M96">
-        <v>38.8777608</v>
+        <v>39.291354</v>
       </c>
       <c r="N96">
-        <v>-33.9507608</v>
+        <v>-34.364354</v>
       </c>
       <c r="O96">
-        <v>-8.487690199999999</v>
+        <v>-8.5910885</v>
       </c>
       <c r="P96">
-        <v>-25.4630706</v>
+        <v>-25.7732655</v>
       </c>
       <c r="Q96">
-        <v>-24.5900706</v>
+        <v>-24.9002655</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6887899885970791</v>
+        <v>0.8173879863164953</v>
       </c>
       <c r="T96">
-        <v>9.356287793560439</v>
+        <v>11.22754535227253</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03168263744243213</v>
+        <v>0.03134913599566968</v>
       </c>
       <c r="W96">
-        <v>0.2283292340910745</v>
+        <v>0.2284078737322211</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1267305497697285</v>
+        <v>0.1253965439826787</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2578568793614348</v>
+        <v>0.2597568793614348</v>
       </c>
       <c r="C97">
-        <v>-116.4561254506515</v>
+        <v>-118.4665339466414</v>
       </c>
       <c r="D97">
-        <v>28.8738745493485</v>
+        <v>28.61746605335857</v>
       </c>
       <c r="E97">
-        <v>123.33</v>
+        <v>125.084</v>
       </c>
       <c r="F97">
-        <v>166.63</v>
+        <v>168.384</v>
       </c>
       <c r="G97">
         <v>21.3</v>
@@ -9241,37 +9241,37 @@
         <v>4.927</v>
       </c>
       <c r="M97">
-        <v>39.291354</v>
+        <v>39.7049472</v>
       </c>
       <c r="N97">
-        <v>-34.364354</v>
+        <v>-34.7779472</v>
       </c>
       <c r="O97">
-        <v>-8.5910885</v>
+        <v>-8.6944868</v>
       </c>
       <c r="P97">
-        <v>-25.7732655</v>
+        <v>-26.0834604</v>
       </c>
       <c r="Q97">
-        <v>-24.9002655</v>
+        <v>-25.2104604</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8173879863164953</v>
+        <v>1.01028498289562</v>
       </c>
       <c r="T97">
-        <v>11.22754535227253</v>
+        <v>14.03443169034067</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03134913599566968</v>
+        <v>0.03102258249571479</v>
       </c>
       <c r="W97">
-        <v>0.2284078737322211</v>
+        <v>0.2284848750475105</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1253965439826787</v>
+        <v>0.1240903299828592</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2597568793614348</v>
+        <v>0.2616568793614348</v>
       </c>
       <c r="C98">
-        <v>-118.4665339466414</v>
+        <v>-120.4724285615466</v>
       </c>
       <c r="D98">
-        <v>28.61746605335857</v>
+        <v>28.3655714384534</v>
       </c>
       <c r="E98">
-        <v>125.084</v>
+        <v>126.838</v>
       </c>
       <c r="F98">
-        <v>168.384</v>
+        <v>170.138</v>
       </c>
       <c r="G98">
         <v>21.3</v>
@@ -9323,37 +9323,37 @@
         <v>4.927</v>
       </c>
       <c r="M98">
-        <v>39.7049472</v>
+        <v>40.11854039999999</v>
       </c>
       <c r="N98">
-        <v>-34.7779472</v>
+        <v>-35.19154039999999</v>
       </c>
       <c r="O98">
-        <v>-8.6944868</v>
+        <v>-8.797885099999998</v>
       </c>
       <c r="P98">
-        <v>-26.0834604</v>
+        <v>-26.3936553</v>
       </c>
       <c r="Q98">
-        <v>-25.2104604</v>
+        <v>-25.52065529999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.010284982895617</v>
+        <v>1.331779977194156</v>
       </c>
       <c r="T98">
-        <v>14.03443169034063</v>
+        <v>18.71257558712085</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03102258249571479</v>
+        <v>0.03070276205761464</v>
       </c>
       <c r="W98">
-        <v>0.2284848750475105</v>
+        <v>0.2285602887068145</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1240903299828592</v>
+        <v>0.1228110482304585</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2616568793614348</v>
+        <v>0.2635568793614348</v>
       </c>
       <c r="C99">
-        <v>-120.4724285615466</v>
+        <v>-122.4739274506338</v>
       </c>
       <c r="D99">
-        <v>28.3655714384534</v>
+        <v>28.11807254936614</v>
       </c>
       <c r="E99">
-        <v>126.838</v>
+        <v>128.592</v>
       </c>
       <c r="F99">
-        <v>170.138</v>
+        <v>171.892</v>
       </c>
       <c r="G99">
         <v>21.3</v>
@@ -9405,37 +9405,37 @@
         <v>4.927</v>
       </c>
       <c r="M99">
-        <v>40.11854039999999</v>
+        <v>40.53213359999999</v>
       </c>
       <c r="N99">
-        <v>-35.19154039999999</v>
+        <v>-35.60513359999999</v>
       </c>
       <c r="O99">
-        <v>-8.797885099999998</v>
+        <v>-8.901283399999999</v>
       </c>
       <c r="P99">
-        <v>-26.3936553</v>
+        <v>-26.7038502</v>
       </c>
       <c r="Q99">
-        <v>-25.52065529999999</v>
+        <v>-25.8308502</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.331779977194156</v>
+        <v>1.974769965791234</v>
       </c>
       <c r="T99">
-        <v>18.71257558712085</v>
+        <v>28.06886338068127</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03070276205761464</v>
+        <v>0.03038946856723082</v>
       </c>
       <c r="W99">
-        <v>0.2285602887068145</v>
+        <v>0.228634163311847</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1228110482304585</v>
+        <v>0.1215578742689233</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2635568793614348</v>
+        <v>0.2654568793614347</v>
       </c>
       <c r="C100">
-        <v>-122.4739274506338</v>
+        <v>-124.4711446810666</v>
       </c>
       <c r="D100">
-        <v>28.11807254936614</v>
+        <v>27.87485531893337</v>
       </c>
       <c r="E100">
-        <v>128.592</v>
+        <v>130.346</v>
       </c>
       <c r="F100">
-        <v>171.892</v>
+        <v>173.646</v>
       </c>
       <c r="G100">
         <v>21.3</v>
@@ -9487,37 +9487,37 @@
         <v>4.927</v>
       </c>
       <c r="M100">
-        <v>40.53213359999999</v>
+        <v>40.9457268</v>
       </c>
       <c r="N100">
-        <v>-35.60513359999999</v>
+        <v>-36.0187268</v>
       </c>
       <c r="O100">
-        <v>-8.901283399999999</v>
+        <v>-9.004681699999999</v>
       </c>
       <c r="P100">
-        <v>-26.7038502</v>
+        <v>-27.0140451</v>
       </c>
       <c r="Q100">
-        <v>-25.8308502</v>
+        <v>-26.1410451</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.974769965791234</v>
+        <v>3.903739931582468</v>
       </c>
       <c r="T100">
-        <v>28.06886338068127</v>
+        <v>56.13772676136254</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03038946856723082</v>
+        <v>0.03008250423826889</v>
       </c>
       <c r="W100">
-        <v>0.228634163311847</v>
+        <v>0.2287065455006162</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1215578742689233</v>
+        <v>0.1203300169530755</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2654568793614347</v>
-      </c>
-      <c r="C101">
-        <v>-124.4711446810666</v>
-      </c>
-      <c r="D101">
-        <v>27.87485531893337</v>
-      </c>
-      <c r="E101">
-        <v>130.346</v>
-      </c>
-      <c r="F101">
-        <v>173.646</v>
-      </c>
-      <c r="G101">
-        <v>21.3</v>
-      </c>
-      <c r="H101">
-        <v>132.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.8</v>
-      </c>
-      <c r="K101">
-        <v>0.873</v>
-      </c>
-      <c r="L101">
-        <v>4.927</v>
-      </c>
-      <c r="M101">
-        <v>40.9457268</v>
-      </c>
-      <c r="N101">
-        <v>-36.0187268</v>
-      </c>
-      <c r="O101">
-        <v>-9.004681699999999</v>
-      </c>
-      <c r="P101">
-        <v>-27.0140451</v>
-      </c>
-      <c r="Q101">
-        <v>-26.1410451</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.903739931582468</v>
-      </c>
-      <c r="T101">
-        <v>56.13772676136254</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03008250423826889</v>
-      </c>
-      <c r="W101">
-        <v>0.2287065455006162</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1203300169530755</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
